--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>21541</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>99.4499969482422</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>95.8000030517578</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>96.9499969482422</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>96.0999984741211</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>142165</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>97.6999969482422</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>90.4499969482422</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>96.3499984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>68581</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>99.6999969482422</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>94.9499969482422</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>94.9499969482422</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>95</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>32765</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>98.5999984741211</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>94.8499984741211</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>94.9499969482422</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>98.5999984741211</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>6987</v>
+        <v>20741</v>
       </c>
       <c r="C2715" t="n">
-        <v>96.25</v>
+        <v>99.5</v>
       </c>
       <c r="D2715" t="n">
-        <v>94.5999984741211</v>
+        <v>95.4000015258789</v>
       </c>
       <c r="E2715" t="n">
+        <v>96.8499984741211</v>
+      </c>
+      <c r="F2715" t="n">
         <v>95.9499969482422</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>95.4000015258789</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>13707</v>
+        <v>6987</v>
       </c>
       <c r="C2716" t="n">
-        <v>96</v>
+        <v>96.25</v>
       </c>
       <c r="D2716" t="n">
-        <v>94.25</v>
+        <v>94.5999984741211</v>
       </c>
       <c r="E2716" t="n">
+        <v>95.9499969482422</v>
+      </c>
+      <c r="F2716" t="n">
         <v>95.4000015258789</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>94.6999969482422</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>25373</v>
+        <v>13707</v>
       </c>
       <c r="C2717" t="n">
-        <v>97.25</v>
+        <v>96</v>
       </c>
       <c r="D2717" t="n">
-        <v>93.5999984741211</v>
+        <v>94.25</v>
       </c>
       <c r="E2717" t="n">
-        <v>95.0999984741211</v>
+        <v>95.4000015258789</v>
       </c>
       <c r="F2717" t="n">
-        <v>97.25</v>
+        <v>94.6999969482422</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>24464</v>
+        <v>25373</v>
       </c>
       <c r="C2718" t="n">
-        <v>98.4499969482422</v>
+        <v>97.25</v>
       </c>
       <c r="D2718" t="n">
-        <v>96.1500015258789</v>
+        <v>93.5999984741211</v>
       </c>
       <c r="E2718" t="n">
-        <v>97.3499984741211</v>
+        <v>95.0999984741211</v>
       </c>
       <c r="F2718" t="n">
-        <v>97.5500030517578</v>
+        <v>97.25</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>21541</v>
+        <v>24464</v>
       </c>
       <c r="C2719" t="n">
-        <v>99.4499969482422</v>
+        <v>98.4499969482422</v>
       </c>
       <c r="D2719" t="n">
-        <v>95.8000030517578</v>
+        <v>96.1500015258789</v>
       </c>
       <c r="E2719" t="n">
-        <v>96.9499969482422</v>
+        <v>97.3499984741211</v>
       </c>
       <c r="F2719" t="n">
-        <v>96.0999984741211</v>
+        <v>97.5500030517578</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>142165</v>
+        <v>21541</v>
       </c>
       <c r="C2720" t="n">
-        <v>97.6999969482422</v>
+        <v>99.4499969482422</v>
       </c>
       <c r="D2720" t="n">
-        <v>90.4499969482422</v>
+        <v>95.8000030517578</v>
       </c>
       <c r="E2720" t="n">
-        <v>96.3499984741211</v>
+        <v>96.9499969482422</v>
       </c>
       <c r="F2720" t="n">
-        <v>94.5</v>
+        <v>96.0999984741211</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>68581</v>
+        <v>142165</v>
       </c>
       <c r="C2721" t="n">
-        <v>99.6999969482422</v>
+        <v>97.6999969482422</v>
       </c>
       <c r="D2721" t="n">
-        <v>94.9499969482422</v>
+        <v>90.4499969482422</v>
       </c>
       <c r="E2721" t="n">
-        <v>94.9499969482422</v>
+        <v>96.3499984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>32765</v>
+        <v>68581</v>
       </c>
       <c r="C2722" t="n">
-        <v>98.5999984741211</v>
+        <v>99.6999969482422</v>
       </c>
       <c r="D2722" t="n">
-        <v>94.8499984741211</v>
+        <v>94.9499969482422</v>
       </c>
       <c r="E2722" t="n">
         <v>94.9499969482422</v>
       </c>
       <c r="F2722" t="n">
+        <v>95</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>49207</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>99.6999969482422</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>97.8000030517578</v>
+      </c>
+      <c r="E2723" t="n">
         <v>98.5999984741211</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>98.6500015258789</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.3669147491455</v>
+        <v>13.3669137954712</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>13.0737056732178</v>
+        <v>13.0737047195435</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G7" t="n">
-        <v>12.6856346130371</v>
+        <v>12.6856327056885</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G8" t="n">
-        <v>12.8753566741943</v>
+        <v>12.875358581543</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.7632474899292</v>
+        <v>12.7632484436035</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G11" t="n">
-        <v>12.9271011352539</v>
+        <v>12.9270992279053</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>12.8494844436646</v>
+        <v>12.8494853973389</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>12.6770086288452</v>
+        <v>12.6770095825195</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>12.0733423233032</v>
+        <v>12.0733413696289</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>12.6770086288452</v>
+        <v>12.6770095825195</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>12.5476531982422</v>
+        <v>12.5476522445679</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G19" t="n">
-        <v>12.5131559371948</v>
+        <v>12.5131568908691</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4355430603027</v>
+        <v>12.4355421066284</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>12.1595802307129</v>
+        <v>12.1595811843872</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0129747390747</v>
+        <v>12.012975692749</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9784812927246</v>
+        <v>11.9784803390503</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G28" t="n">
-        <v>10.8315124511719</v>
+        <v>10.8315114974976</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>11.2109603881836</v>
+        <v>11.2109594345093</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G30" t="n">
-        <v>11.2971992492676</v>
+        <v>11.2972002029419</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>11.7283887863159</v>
+        <v>11.7283916473389</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G34" t="n">
-        <v>11.8146257400513</v>
+        <v>11.8146276473999</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>11.7715072631836</v>
+        <v>11.7715101242065</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G36" t="n">
-        <v>11.9784812927246</v>
+        <v>11.9784803390503</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G37" t="n">
-        <v>11.8491230010986</v>
+        <v>11.8491220474243</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G38" t="n">
-        <v>11.8491230010986</v>
+        <v>11.8491220474243</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G39" t="n">
-        <v>11.9181127548218</v>
+        <v>11.9181137084961</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G40" t="n">
-        <v>11.8146257400513</v>
+        <v>11.8146276473999</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6680202484131</v>
+        <v>11.668023109436</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>14.5</v>
       </c>
       <c r="G47" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>14.5</v>
       </c>
       <c r="G49" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>12.6252670288086</v>
+        <v>12.6252660751343</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G52" t="n">
-        <v>12.9874658584595</v>
+        <v>12.9874668121338</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G53" t="n">
-        <v>12.9788427352905</v>
+        <v>12.9788436889648</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>13.0133380889893</v>
+        <v>13.0133361816406</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.8753566741943</v>
+        <v>12.875358581543</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G60" t="n">
-        <v>12.5821475982666</v>
+        <v>12.5821466445923</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.75</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7201271057129</v>
+        <v>12.7201280593872</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>12.6770086288452</v>
+        <v>12.6770095825195</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>12.7287530899048</v>
+        <v>12.7287521362305</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>12.7632474899292</v>
+        <v>12.7632484436035</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>14.75</v>
       </c>
       <c r="G65" t="n">
-        <v>12.7201271057129</v>
+        <v>12.7201280593872</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>13.0219631195068</v>
+        <v>13.0219621658325</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.9788427352905</v>
+        <v>12.9788436889648</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G73" t="n">
-        <v>13.0133380889893</v>
+        <v>13.0133361816406</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G74" t="n">
-        <v>12.9788427352905</v>
+        <v>12.9788436889648</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G75" t="n">
-        <v>13.0133380889893</v>
+        <v>13.0133361816406</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>12.8063659667969</v>
+        <v>12.8063669204712</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G81" t="n">
-        <v>13.522144317627</v>
+        <v>13.5221433639526</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G82" t="n">
-        <v>13.522144317627</v>
+        <v>13.5221433639526</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G83" t="n">
-        <v>13.2892999649048</v>
+        <v>13.2893009185791</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>13.2806749343872</v>
+        <v>13.2806768417358</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G85" t="n">
-        <v>13.0305862426758</v>
+        <v>13.0305843353271</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G86" t="n">
-        <v>13.1426935195923</v>
+        <v>13.1426963806152</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G91" t="n">
-        <v>13.0133380889893</v>
+        <v>13.0133361816406</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>12.918475151062</v>
+        <v>12.9184741973877</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="n">
-        <v>12.9357242584229</v>
+        <v>12.9357233047485</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G94" t="n">
-        <v>12.8236131668091</v>
+        <v>12.8236141204834</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>12.6770086288452</v>
+        <v>12.6770095825195</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>14.5</v>
       </c>
       <c r="G96" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G99" t="n">
-        <v>12.2113218307495</v>
+        <v>12.2113237380981</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8663711547852</v>
+        <v>11.8663692474365</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>11.9871044158936</v>
+        <v>11.9871034622192</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G103" t="n">
-        <v>12.271689414978</v>
+        <v>12.2716875076294</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G104" t="n">
-        <v>12.3924217224121</v>
+        <v>12.3924236297607</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>12.4614124298096</v>
+        <v>12.4614133834839</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>11.9871044158936</v>
+        <v>11.9871034622192</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G111" t="n">
-        <v>12.2026996612549</v>
+        <v>12.2026977539062</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G113" t="n">
-        <v>12.5993947982788</v>
+        <v>12.5993928909302</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G115" t="n">
-        <v>12.5821475982666</v>
+        <v>12.5821466445923</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G116" t="n">
-        <v>12.271689414978</v>
+        <v>12.2716875076294</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G119" t="n">
-        <v>12.0819673538208</v>
+        <v>12.0819664001465</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G120" t="n">
-        <v>12.2113218307495</v>
+        <v>12.2113237380981</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>12.2458181381226</v>
+        <v>12.2458190917969</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>12.2458181381226</v>
+        <v>12.2458190917969</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G125" t="n">
-        <v>11.6593999862671</v>
+        <v>11.6593990325928</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>11.6852703094482</v>
+        <v>11.6852712631226</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G128" t="n">
-        <v>12.0905895233154</v>
+        <v>12.0905904769897</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>11.9871044158936</v>
+        <v>11.9871034622192</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>11.8146257400513</v>
+        <v>11.8146276473999</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G133" t="n">
-        <v>12.0560922622681</v>
+        <v>12.0560941696167</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G134" t="n">
-        <v>12.021598815918</v>
+        <v>12.0215997695923</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>12.1595802307129</v>
+        <v>12.1595811843872</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>14.5</v>
       </c>
       <c r="G140" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>12.2458181381226</v>
+        <v>12.2458190917969</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>14.5</v>
       </c>
       <c r="G142" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G143" t="n">
-        <v>12.6080188751221</v>
+        <v>12.6080179214478</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G144" t="n">
-        <v>12.6080188751221</v>
+        <v>12.6080179214478</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>12.5562753677368</v>
+        <v>12.5562772750854</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>12.7632474899292</v>
+        <v>12.7632484436035</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>12.8063659667969</v>
+        <v>12.8063669204712</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G148" t="n">
-        <v>12.7028799057007</v>
+        <v>12.7028789520264</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>14.5</v>
       </c>
       <c r="G149" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>14.5</v>
       </c>
       <c r="G150" t="n">
-        <v>12.5045337677002</v>
+        <v>12.5045318603516</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>12.6338891983032</v>
+        <v>12.6338901519775</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>12.6338891983032</v>
+        <v>12.6338901519775</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G153" t="n">
-        <v>12.6080188751221</v>
+        <v>12.6080179214478</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>12.6770086288452</v>
+        <v>12.6770095825195</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G155" t="n">
-        <v>12.5821475982666</v>
+        <v>12.5821466445923</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>12.7632474899292</v>
+        <v>12.7632484436035</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>12.5907707214355</v>
+        <v>12.5907716751099</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>12.6942577362061</v>
+        <v>12.6942558288574</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>14.75</v>
       </c>
       <c r="G159" t="n">
-        <v>12.7201271057129</v>
+        <v>12.7201280593872</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6856346130371</v>
+        <v>12.6856327056885</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>12.8494844436646</v>
+        <v>12.8494853973389</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G163" t="n">
-        <v>12.6597604751587</v>
+        <v>12.6597623825073</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G164" t="n">
-        <v>12.3665533065796</v>
+        <v>12.366551399231</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G165" t="n">
-        <v>12.5907707214355</v>
+        <v>12.5907716751099</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G166" t="n">
-        <v>12.6856346130371</v>
+        <v>12.6856327056885</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>12.6338891983032</v>
+        <v>12.6338901519775</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>12.7632474899292</v>
+        <v>12.7632484436035</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G169" t="n">
-        <v>13.0047149658203</v>
+        <v>13.0047130584717</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G170" t="n">
-        <v>12.8581075668335</v>
+        <v>12.8581085205078</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G171" t="n">
-        <v>12.6942577362061</v>
+        <v>12.6942558288574</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>13.0823287963867</v>
+        <v>13.082329750061</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>13.1944398880005</v>
+        <v>13.1944389343262</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>13.5048952102661</v>
+        <v>13.5048971176147</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5393896102905</v>
+        <v>13.5393905639648</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>15.25</v>
       </c>
       <c r="G179" t="n">
-        <v>13.5660791397095</v>
+        <v>13.5660772323608</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G180" t="n">
-        <v>13.3881616592407</v>
+        <v>13.3881635665894</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G181" t="n">
-        <v>13.6817235946655</v>
+        <v>13.6817245483398</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G182" t="n">
-        <v>13.4415369033813</v>
+        <v>13.441535949707</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G183" t="n">
-        <v>13.4593276977539</v>
+        <v>13.4593286514282</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>13.4771184921265</v>
+        <v>13.4771203994751</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G185" t="n">
-        <v>13.4593276977539</v>
+        <v>13.4593286514282</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G186" t="n">
-        <v>13.414849281311</v>
+        <v>13.4148483276367</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G187" t="n">
-        <v>13.4326419830322</v>
+        <v>13.4326410293579</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G188" t="n">
-        <v>13.414849281311</v>
+        <v>13.4148483276367</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G189" t="n">
-        <v>13.4326419830322</v>
+        <v>13.4326410293579</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G190" t="n">
-        <v>13.4415369033813</v>
+        <v>13.441535949707</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>13.1657667160034</v>
+        <v>13.1657686233521</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G194" t="n">
-        <v>13.3970584869385</v>
+        <v>13.3970575332642</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G195" t="n">
-        <v>13.3881616592407</v>
+        <v>13.3881635665894</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G198" t="n">
-        <v>13.3881616592407</v>
+        <v>13.3881635665894</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>15.25</v>
       </c>
       <c r="G202" t="n">
-        <v>13.5660791397095</v>
+        <v>13.5660772323608</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>15.5</v>
       </c>
       <c r="G203" t="n">
-        <v>13.7884731292725</v>
+        <v>13.7884721755981</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>13.8507432937622</v>
+        <v>13.8507423400879</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G205" t="n">
-        <v>13.8240556716919</v>
+        <v>13.8240566253662</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>15.5</v>
       </c>
       <c r="G206" t="n">
-        <v>13.7884731292725</v>
+        <v>13.7884721755981</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G207" t="n">
-        <v>13.717306137085</v>
+        <v>13.7173070907593</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>14.170991897583</v>
+        <v>14.1709928512573</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3222198486328</v>
+        <v>14.3222208023071</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G216" t="n">
-        <v>14.4645519256592</v>
+        <v>14.4645528793335</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G217" t="n">
-        <v>14.197678565979</v>
+        <v>14.1976776123047</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G218" t="n">
-        <v>14.1176176071167</v>
+        <v>14.1176166534424</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G220" t="n">
-        <v>14.170991897583</v>
+        <v>14.1709928512573</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G221" t="n">
-        <v>14.3489065170288</v>
+        <v>14.3489074707031</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G222" t="n">
-        <v>14.3489065170288</v>
+        <v>14.3489074707031</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G224" t="n">
-        <v>14.4467611312866</v>
+        <v>14.4467620849609</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G226" t="n">
-        <v>14.5357189178467</v>
+        <v>14.535719871521</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G227" t="n">
-        <v>14.5179271697998</v>
+        <v>14.5179281234741</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G231" t="n">
-        <v>14.6246767044067</v>
+        <v>14.6246776580811</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>14.5446138381958</v>
+        <v>14.5446157455444</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G234" t="n">
-        <v>14.4645519256592</v>
+        <v>14.4645528793335</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>14.3844919204712</v>
+        <v>14.3844890594482</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G236" t="n">
-        <v>14.3844919204712</v>
+        <v>14.3844890594482</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>14.3222198486328</v>
+        <v>14.3222208023071</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>14.5001363754272</v>
+        <v>14.5001344680786</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>16.25</v>
       </c>
       <c r="G243" t="n">
-        <v>14.4556589126587</v>
+        <v>14.4556579589844</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>14.5446138381958</v>
+        <v>14.5446157455444</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>14.7225294113159</v>
+        <v>14.7225284576416</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G247" t="n">
-        <v>14.847071647644</v>
+        <v>14.8470726013184</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>15.1673212051392</v>
+        <v>15.1673183441162</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>17.25</v>
       </c>
       <c r="G250" t="n">
-        <v>15.3452367782593</v>
+        <v>15.3452348709106</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G251" t="n">
-        <v>15.7099637985229</v>
+        <v>15.7099647521973</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.5</v>
       </c>
       <c r="G252" t="n">
-        <v>15.5676288604736</v>
+        <v>15.5676298141479</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>15.656587600708</v>
+        <v>15.6565885543823</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G254" t="n">
-        <v>15.6210050582886</v>
+        <v>15.6210041046143</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G255" t="n">
-        <v>15.4964656829834</v>
+        <v>15.4964647293091</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>17.5</v>
       </c>
       <c r="G256" t="n">
-        <v>15.5676288604736</v>
+        <v>15.5676298141479</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G257" t="n">
-        <v>15.7366495132446</v>
+        <v>15.7366552352905</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G259" t="n">
-        <v>16.644021987915</v>
+        <v>16.6440181732178</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G260" t="n">
-        <v>16.8575191497803</v>
+        <v>16.8575210571289</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G261" t="n">
-        <v>16.9197902679443</v>
+        <v>16.919792175293</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>16.9909572601318</v>
+        <v>16.9909591674805</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G263" t="n">
-        <v>16.7507705688477</v>
+        <v>16.7507724761963</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>18.75</v>
       </c>
       <c r="G264" t="n">
-        <v>16.6796016693115</v>
+        <v>16.6796035766602</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G266" t="n">
-        <v>16.8041458129883</v>
+        <v>16.804141998291</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G267" t="n">
-        <v>17.0443363189697</v>
+        <v>17.0443325042725</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G268" t="n">
-        <v>17.2400379180908</v>
+        <v>17.2400360107422</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>17.0888080596924</v>
+        <v>17.088809967041</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G270" t="n">
-        <v>16.9375839233398</v>
+        <v>16.9375820159912</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G272" t="n">
-        <v>17.3378925323486</v>
+        <v>17.337890625</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>17.3289985656738</v>
+        <v>17.3289966583252</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G274" t="n">
-        <v>17.2400379180908</v>
+        <v>17.2400360107422</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G275" t="n">
-        <v>17.0087490081787</v>
+        <v>17.0087509155273</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G276" t="n">
-        <v>17.0443363189697</v>
+        <v>17.0443325042725</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>16.9909572601318</v>
+        <v>16.9909591674805</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G279" t="n">
-        <v>16.6262283325195</v>
+        <v>16.6262302398682</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G280" t="n">
-        <v>16.6173324584961</v>
+        <v>16.6173343658447</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>16.9375839233398</v>
+        <v>16.9375820159912</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G285" t="n">
-        <v>16.4661064147949</v>
+        <v>16.4661045074463</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G286" t="n">
-        <v>16.6351261138916</v>
+        <v>16.6351222991943</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G287" t="n">
-        <v>16.6173324584961</v>
+        <v>16.6173343658447</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6351261138916</v>
+        <v>16.6351222991943</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>16.8130416870117</v>
+        <v>16.8130397796631</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>18.75</v>
       </c>
       <c r="G292" t="n">
-        <v>16.6796016693115</v>
+        <v>16.6796035766602</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>16.5906448364258</v>
+        <v>16.5906467437744</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G295" t="n">
-        <v>16.6173324584961</v>
+        <v>16.6173343658447</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>16.5461654663086</v>
+        <v>16.5461692810059</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G297" t="n">
-        <v>16.5906448364258</v>
+        <v>16.5906467437744</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G299" t="n">
-        <v>16.9375839233398</v>
+        <v>16.9375820159912</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G300" t="n">
-        <v>16.9642658233643</v>
+        <v>16.9642715454102</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>19.25</v>
       </c>
       <c r="G301" t="n">
-        <v>17.1243934631348</v>
+        <v>17.124397277832</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>17.5247077941895</v>
+        <v>17.5247039794922</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>17.7026214599609</v>
+        <v>17.7026195526123</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.25</v>
       </c>
       <c r="G310" t="n">
-        <v>18.0139713287354</v>
+        <v>18.0139751434326</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21</v>
       </c>
       <c r="G313" t="n">
-        <v>18.6811580657959</v>
+        <v>18.6811561584473</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>18.3698043823242</v>
+        <v>18.3698024749756</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0369873046875</v>
+        <v>19.0369892120361</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>21.4699993133545</v>
       </c>
       <c r="G316" t="n">
-        <v>19.0992565155029</v>
+        <v>19.0992584228516</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G317" t="n">
-        <v>19.0903587341309</v>
+        <v>19.0903625488281</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G318" t="n">
-        <v>19.4017181396484</v>
+        <v>19.4017143249512</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3839244842529</v>
+        <v>19.3839225769043</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>18.8768634796143</v>
+        <v>18.8768615722656</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G325" t="n">
-        <v>18.9391345977783</v>
+        <v>18.9391326904297</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G326" t="n">
-        <v>18.6989498138428</v>
+        <v>18.6989517211914</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G327" t="n">
-        <v>18.654468536377</v>
+        <v>18.6544704437256</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G328" t="n">
-        <v>18.8323841094971</v>
+        <v>18.8323879241943</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>18.3698043823242</v>
+        <v>18.3698024749756</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G331" t="n">
-        <v>17.9517002105713</v>
+        <v>17.9517040252686</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G333" t="n">
-        <v>18.5833034515381</v>
+        <v>18.5833015441895</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>21.5</v>
       </c>
       <c r="G335" t="n">
-        <v>19.1259460449219</v>
+        <v>19.1259441375732</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>20.0866928100586</v>
+        <v>20.08669090271</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>20.5492744445801</v>
+        <v>20.5492725372314</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>20.9940605163574</v>
+        <v>20.9940586090088</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>20.9940605163574</v>
+        <v>20.9940586090088</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>20.5937538146973</v>
+        <v>20.5937519073486</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>20.8161449432373</v>
+        <v>20.8161468505859</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>20.7271900177002</v>
+        <v>20.7271881103516</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>20.3268775939941</v>
+        <v>20.3268795013428</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9176712036133</v>
+        <v>19.9176731109619</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3713569641113</v>
+        <v>20.3713531494141</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>21.0830249786377</v>
+        <v>21.0830192565918</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>25.0900001525879</v>
       </c>
       <c r="G355" t="n">
-        <v>22.3195343017578</v>
+        <v>22.3195381164551</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>25.1900005340576</v>
       </c>
       <c r="G356" t="n">
-        <v>22.4084949493408</v>
+        <v>22.4084930419922</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>23.7517585754395</v>
+        <v>23.7517566680908</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G363" t="n">
-        <v>23.5382556915283</v>
+        <v>23.538257598877</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>23.484884262085</v>
+        <v>23.4848823547363</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G365" t="n">
-        <v>23.1913204193115</v>
+        <v>23.1913223266602</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>25.5</v>
       </c>
       <c r="G366" t="n">
-        <v>22.6842594146729</v>
+        <v>22.6842613220215</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>24.9300003051758</v>
       </c>
       <c r="G367" t="n">
-        <v>22.1772003173828</v>
+        <v>22.1771984100342</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>25</v>
       </c>
       <c r="G368" t="n">
-        <v>22.2394695281982</v>
+        <v>22.2394714355469</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>22.3995971679688</v>
+        <v>22.3995952606201</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>24.9099998474121</v>
       </c>
       <c r="G372" t="n">
-        <v>22.1594085693359</v>
+        <v>22.1594104766846</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>21.8836441040039</v>
+        <v>21.8836402893066</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>22.417387008667</v>
+        <v>22.4173927307129</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>25.1900005340576</v>
       </c>
       <c r="G377" t="n">
-        <v>22.4084949493408</v>
+        <v>22.4084930419922</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25</v>
       </c>
       <c r="G378" t="n">
-        <v>22.2394695281982</v>
+        <v>22.2394714355469</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>22.0615558624268</v>
+        <v>22.0615520477295</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>25.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>22.3195343017578</v>
+        <v>22.3195381164551</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G381" t="n">
-        <v>22.0615558624268</v>
+        <v>22.0615520477295</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G384" t="n">
-        <v>21.9103298187256</v>
+        <v>21.910327911377</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>23.8299999237061</v>
       </c>
       <c r="G386" t="n">
-        <v>21.1986656188965</v>
+        <v>21.1986637115479</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>21.6256637573242</v>
+        <v>21.6256618499756</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G388" t="n">
-        <v>21.581184387207</v>
+        <v>21.5811824798584</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>24.0699996948242</v>
       </c>
       <c r="G389" t="n">
-        <v>21.4121646881104</v>
+        <v>21.4121627807617</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G392" t="n">
-        <v>21.9992828369141</v>
+        <v>21.9992866516113</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>22.5063457489014</v>
+        <v>22.5063438415527</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>24.75</v>
       </c>
       <c r="G394" t="n">
-        <v>22.0170803070068</v>
+        <v>22.0170764923096</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>24.75</v>
       </c>
       <c r="G395" t="n">
-        <v>22.0170803070068</v>
+        <v>22.0170764923096</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G396" t="n">
-        <v>21.8925342559814</v>
+        <v>21.8925361633301</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>24.7900009155273</v>
       </c>
       <c r="G397" t="n">
-        <v>22.0526599884033</v>
+        <v>22.052661895752</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G398" t="n">
-        <v>22.2216796875</v>
+        <v>22.2216777801514</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G399" t="n">
-        <v>22.0615558624268</v>
+        <v>22.0615520477295</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G400" t="n">
-        <v>22.3017444610596</v>
+        <v>22.3017406463623</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>22.3284282684326</v>
+        <v>22.3284320831299</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>21.8836441040039</v>
+        <v>21.8836402893066</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G404" t="n">
-        <v>21.9459095001221</v>
+        <v>21.9459133148193</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>21.9281196594238</v>
+        <v>21.9281215667725</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G406" t="n">
-        <v>21.8302631378174</v>
+        <v>21.8302669525146</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G408" t="n">
-        <v>21.7857894897461</v>
+        <v>21.7857875823975</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G409" t="n">
-        <v>21.7857894897461</v>
+        <v>21.7857875823975</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>21.8836441040039</v>
+        <v>21.8836402893066</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.7900009155273</v>
       </c>
       <c r="G411" t="n">
-        <v>22.0526599884033</v>
+        <v>22.052661895752</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24.75</v>
       </c>
       <c r="G412" t="n">
-        <v>22.0170803070068</v>
+        <v>22.0170764923096</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>21.9014339447021</v>
+        <v>21.9014320373535</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>21.9281196594238</v>
+        <v>21.9281215667725</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G418" t="n">
-        <v>21.9014339447021</v>
+        <v>21.9014320373535</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>21.3054141998291</v>
+        <v>21.3054122924805</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G425" t="n">
-        <v>21.0385398864746</v>
+        <v>21.038537979126</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>21.8302631378174</v>
+        <v>21.8302669525146</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>21.7324161529541</v>
+        <v>21.7324123382568</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>21.3943729400635</v>
+        <v>21.3943710327148</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>21.8836441040039</v>
+        <v>21.8836402893066</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>21.8836441040039</v>
+        <v>21.8836402893066</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G438" t="n">
-        <v>22.2216796875</v>
+        <v>22.2216777801514</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>22.3284282684326</v>
+        <v>22.3284320831299</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>25.1299991607666</v>
       </c>
       <c r="G442" t="n">
-        <v>22.3551197052002</v>
+        <v>22.3551158905029</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G445" t="n">
-        <v>22.9567260742188</v>
+        <v>22.9567241668701</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G447" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>27.3799991607666</v>
       </c>
       <c r="G449" t="n">
-        <v>24.9031352996826</v>
+        <v>24.9031314849854</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>28</v>
       </c>
       <c r="G450" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>28</v>
       </c>
       <c r="G451" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G452" t="n">
-        <v>25.4488525390625</v>
+        <v>25.4488544464111</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>28</v>
       </c>
       <c r="G453" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G454" t="n">
-        <v>25.4488525390625</v>
+        <v>25.4488544464111</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>28</v>
       </c>
       <c r="G455" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G456" t="n">
-        <v>25.3397102355957</v>
+        <v>25.3397121429443</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>27.8400001525879</v>
       </c>
       <c r="G457" t="n">
-        <v>25.3215198516846</v>
+        <v>25.3215217590332</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>28</v>
       </c>
       <c r="G458" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>28.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>25.6580467224121</v>
+        <v>25.6580486297607</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G460" t="n">
-        <v>25.5398082733154</v>
+        <v>25.5398101806641</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G461" t="n">
-        <v>25.6307640075684</v>
+        <v>25.630765914917</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>25.7399082183838</v>
+        <v>25.7399044036865</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>25.5580024719238</v>
+        <v>25.5580005645752</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>28</v>
       </c>
       <c r="G464" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>28</v>
       </c>
       <c r="G465" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>25.3306159973145</v>
+        <v>25.3306179046631</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G470" t="n">
-        <v>24.7394180297852</v>
+        <v>24.7394161224365</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>24.9213237762451</v>
+        <v>24.9213218688965</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>27.4699993133545</v>
       </c>
       <c r="G473" t="n">
-        <v>24.9849910736084</v>
+        <v>24.984992980957</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>24.4665565490723</v>
+        <v>24.4665546417236</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G477" t="n">
-        <v>24.5211277008057</v>
+        <v>24.521125793457</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>27</v>
       </c>
       <c r="G479" t="n">
-        <v>24.5575084686279</v>
+        <v>24.5575122833252</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>22.9203433990479</v>
+        <v>22.9203453063965</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G485" t="n">
-        <v>22.9203433990479</v>
+        <v>22.9203453063965</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>22.474666595459</v>
+        <v>22.4746685028076</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G489" t="n">
-        <v>22.3655242919922</v>
+        <v>22.3655223846436</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>22.1927127838135</v>
+        <v>22.1927108764648</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G493" t="n">
-        <v>22.0198993682861</v>
+        <v>22.0199012756348</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>24.5</v>
       </c>
       <c r="G494" t="n">
-        <v>22.2836685180664</v>
+        <v>22.2836666107178</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>22.8021030426025</v>
+        <v>22.8020992279053</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>22.1927127838135</v>
+        <v>22.1927108764648</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G498" t="n">
-        <v>23.084056854248</v>
+        <v>23.0840587615967</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>25.7900009155273</v>
       </c>
       <c r="G499" t="n">
-        <v>23.4569702148438</v>
+        <v>23.4569683074951</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G501" t="n">
-        <v>22.8293876647949</v>
+        <v>22.8293895721436</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>24.9300003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>22.674768447876</v>
+        <v>22.6747665405273</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>24.5</v>
       </c>
       <c r="G503" t="n">
-        <v>22.2836685180664</v>
+        <v>22.2836666107178</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G505" t="n">
-        <v>22.4291934967041</v>
+        <v>22.4291915893555</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>22.1927127838135</v>
+        <v>22.1927108764648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G507" t="n">
-        <v>22.3837146759033</v>
+        <v>22.3837127685547</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>26.0100002288818</v>
       </c>
       <c r="G510" t="n">
-        <v>23.6570682525635</v>
+        <v>23.6570701599121</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>23.7389259338379</v>
+        <v>23.7389278411865</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>23.9208335876465</v>
+        <v>23.9208354949951</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>24.0572662353516</v>
+        <v>24.0572643280029</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>24.2846508026123</v>
+        <v>24.2846488952637</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>27</v>
       </c>
       <c r="G518" t="n">
-        <v>24.5575084686279</v>
+        <v>24.5575122833252</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>25.512523651123</v>
+        <v>25.5125217437744</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>25.5580024719238</v>
+        <v>25.5580005645752</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>25.2851409912109</v>
+        <v>25.2851390838623</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>24.8758487701416</v>
+        <v>24.875846862793</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>24.8303699493408</v>
+        <v>24.8303737640381</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>25.1032333374023</v>
+        <v>25.1032314300537</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G528" t="n">
-        <v>24.4665565490723</v>
+        <v>24.4665546417236</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>25.1941871643066</v>
+        <v>25.194185256958</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>27.25</v>
       </c>
       <c r="G531" t="n">
-        <v>24.7848949432373</v>
+        <v>24.7848968505859</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G533" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>26.5</v>
       </c>
       <c r="G534" t="n">
-        <v>24.1027412414551</v>
+        <v>24.1027374267578</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>26.5</v>
       </c>
       <c r="G535" t="n">
-        <v>24.1027412414551</v>
+        <v>24.1027374267578</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>23.3296318054199</v>
+        <v>23.3296337127686</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>23.6934471130371</v>
+        <v>23.6934490203857</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>26.5</v>
       </c>
       <c r="G541" t="n">
-        <v>24.1027412414551</v>
+        <v>24.1027374267578</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>26.5</v>
       </c>
       <c r="G545" t="n">
-        <v>24.1027412414551</v>
+        <v>24.1027374267578</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>26.25</v>
       </c>
       <c r="G548" t="n">
-        <v>23.8753566741943</v>
+        <v>23.8753547668457</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>23.9208335876465</v>
+        <v>23.9208354949951</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G550" t="n">
-        <v>23.9663143157959</v>
+        <v>23.9663124084473</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>24.4210796356201</v>
+        <v>24.4210777282715</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>23.9208335876465</v>
+        <v>23.9208354949951</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>24.4665565490723</v>
+        <v>24.4665546417236</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>23.9663143157959</v>
+        <v>23.9663124084473</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>24.2846508026123</v>
+        <v>24.2846488952637</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>24.6484622955322</v>
+        <v>24.6484642028809</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>25.1487083435059</v>
+        <v>25.1487102508545</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>25.2851409912109</v>
+        <v>25.2851390838623</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>25.5580024719238</v>
+        <v>25.5580005645752</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>25.3760948181152</v>
+        <v>25.3760929107666</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>25.1032333374023</v>
+        <v>25.1032314300537</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G567" t="n">
-        <v>24.8303699493408</v>
+        <v>24.8303737640381</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>26.5</v>
       </c>
       <c r="G569" t="n">
-        <v>24.1027412414551</v>
+        <v>24.1027374267578</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>23.6934471130371</v>
+        <v>23.6934490203857</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>27</v>
       </c>
       <c r="G572" t="n">
-        <v>24.5575084686279</v>
+        <v>24.5575122833252</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>24.4665565490723</v>
+        <v>24.4665546417236</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>23.9208335876465</v>
+        <v>23.9208354949951</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G578" t="n">
-        <v>23.9663143157959</v>
+        <v>23.9663124084473</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>23.6934471130371</v>
+        <v>23.6934490203857</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G580" t="n">
-        <v>24.0572662353516</v>
+        <v>24.0572643280029</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>23.9208335876465</v>
+        <v>23.9208354949951</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>27.25</v>
       </c>
       <c r="G586" t="n">
-        <v>24.7848949432373</v>
+        <v>24.7848968505859</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>24.4665565490723</v>
+        <v>24.4665546417236</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>27</v>
       </c>
       <c r="G589" t="n">
-        <v>24.5575084686279</v>
+        <v>24.5575122833252</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>25.1032333374023</v>
+        <v>25.1032314300537</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>24.4665565490723</v>
+        <v>24.4665546417236</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>24.0117893218994</v>
+        <v>24.0117874145508</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>23.9208335876465</v>
+        <v>23.9208354949951</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G597" t="n">
-        <v>25.3760948181152</v>
+        <v>25.3760929107666</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>28</v>
       </c>
       <c r="G599" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>25.512523651123</v>
+        <v>25.5125217437744</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>25.1032333374023</v>
+        <v>25.1032314300537</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>25.6489543914795</v>
+        <v>25.6489562988281</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>27.1951656341553</v>
+        <v>27.1951694488525</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>27.1951656341553</v>
+        <v>27.1951694488525</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G606" t="n">
-        <v>27.3770732879639</v>
+        <v>27.3770771026611</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>27.3770732879639</v>
+        <v>27.3770771026611</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>27.6954154968262</v>
+        <v>27.6954135894775</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>27.1496887207031</v>
+        <v>27.1496925354004</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>29</v>
       </c>
       <c r="G610" t="n">
-        <v>26.3765869140625</v>
+        <v>26.3765850067139</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>28</v>
       </c>
       <c r="G612" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>24.1936931610107</v>
+        <v>24.1936950683594</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>24.7394180297852</v>
+        <v>24.7394161224365</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>24.6484622955322</v>
+        <v>24.6484642028809</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>24.7394180297852</v>
+        <v>24.7394161224365</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G620" t="n">
-        <v>24.8758487701416</v>
+        <v>24.875846862793</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G621" t="n">
-        <v>24.8758487701416</v>
+        <v>24.875846862793</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>24.3755989074707</v>
+        <v>24.3756008148193</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>24.9213237762451</v>
+        <v>24.9213218688965</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>25.6489543914795</v>
+        <v>25.6489562988281</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>26.2401561737061</v>
+        <v>26.2401542663574</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>26.1037216186523</v>
+        <v>26.1037254333496</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>25.8763389587402</v>
+        <v>25.8763370513916</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>25.9672908782959</v>
+        <v>25.9672927856445</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>28.5</v>
       </c>
       <c r="G634" t="n">
-        <v>25.921817779541</v>
+        <v>25.9218158721924</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>28.5</v>
       </c>
       <c r="G635" t="n">
-        <v>25.921817779541</v>
+        <v>25.9218158721924</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>28</v>
       </c>
       <c r="G636" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>25.9672908782959</v>
+        <v>25.9672927856445</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G642" t="n">
-        <v>27.0132598876953</v>
+        <v>27.0132617950439</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>26.1946773529053</v>
+        <v>26.1946754455566</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>25.7399082183838</v>
+        <v>25.7399044036865</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>25.5580024719238</v>
+        <v>25.5580005645752</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>26.4675407409668</v>
+        <v>26.4675388336182</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>26.7404022216797</v>
+        <v>26.7403984069824</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>27.0132598876953</v>
+        <v>27.0132617950439</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>26.4675407409668</v>
+        <v>26.4675388336182</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>26.1037216186523</v>
+        <v>26.1037254333496</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>28.5</v>
       </c>
       <c r="G654" t="n">
-        <v>25.921817779541</v>
+        <v>25.9218158721924</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>26.5130176544189</v>
+        <v>26.5130157470703</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>27.3770732879639</v>
+        <v>27.3770771026611</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>27.5589809417725</v>
+        <v>27.5589828491211</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>31.25</v>
       </c>
       <c r="G663" t="n">
-        <v>28.4230461120605</v>
+        <v>28.4230442047119</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>28.3320922851562</v>
+        <v>28.3320903778076</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>30.5</v>
       </c>
       <c r="G666" t="n">
-        <v>27.7408905029297</v>
+        <v>27.7408885955811</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>27.6954154968262</v>
+        <v>27.6954135894775</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>26.6949253082275</v>
+        <v>26.6949214935303</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>29.25</v>
       </c>
       <c r="G670" t="n">
-        <v>26.6039695739746</v>
+        <v>26.603967666626</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G671" t="n">
-        <v>26.7404022216797</v>
+        <v>26.7403984069824</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G672" t="n">
-        <v>26.7858791351318</v>
+        <v>26.7858753204346</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>29.25</v>
       </c>
       <c r="G673" t="n">
-        <v>26.6039695739746</v>
+        <v>26.603967666626</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>26.3311080932617</v>
+        <v>26.3311100006104</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>26.422061920166</v>
+        <v>26.4220600128174</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>25.7399082183838</v>
+        <v>25.7399044036865</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>28.5</v>
       </c>
       <c r="G677" t="n">
-        <v>25.921817779541</v>
+        <v>25.9218158721924</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>26.4675407409668</v>
+        <v>26.4675388336182</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G680" t="n">
-        <v>25.8763389587402</v>
+        <v>25.8763370513916</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G681" t="n">
-        <v>26.1946773529053</v>
+        <v>26.1946754455566</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>28.25</v>
       </c>
       <c r="G683" t="n">
-        <v>25.6944313049316</v>
+        <v>25.6944351196289</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>28</v>
       </c>
       <c r="G684" t="n">
-        <v>25.4670467376709</v>
+        <v>25.4670486450195</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>25.1941871643066</v>
+        <v>25.194185256958</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G686" t="n">
-        <v>25.2851409912109</v>
+        <v>25.2851390838623</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>25.5580024719238</v>
+        <v>25.5580005645752</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>26.1037216186523</v>
+        <v>26.1037254333496</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>30</v>
       </c>
       <c r="G690" t="n">
-        <v>27.2861194610596</v>
+        <v>27.2861213684082</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>26.7404022216797</v>
+        <v>26.7403984069824</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G692" t="n">
-        <v>26.5584926605225</v>
+        <v>26.5584945678711</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>29</v>
       </c>
       <c r="G693" t="n">
-        <v>26.3765869140625</v>
+        <v>26.3765850067139</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.2401561737061</v>
+        <v>26.2401542663574</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>28.5</v>
       </c>
       <c r="G695" t="n">
-        <v>25.921817779541</v>
+        <v>25.9218158721924</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.8763389587402</v>
+        <v>25.8763370513916</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>25.8298835754395</v>
+        <v>25.8298816680908</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>25.7369709014893</v>
+        <v>25.736967086792</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G699" t="n">
-        <v>26.1086235046387</v>
+        <v>26.10862159729</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G702" t="n">
-        <v>25.3653144836426</v>
+        <v>25.3653163909912</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>24.8078384399414</v>
+        <v>24.8078346252441</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G704" t="n">
-        <v>25.3653144836426</v>
+        <v>25.3653163909912</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>24.9936637878418</v>
+        <v>24.9936618804932</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>26</v>
       </c>
       <c r="G707" t="n">
-        <v>24.1574440002441</v>
+        <v>24.1574420928955</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.9495697021484</v>
+        <v>22.9495716094971</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>24.5</v>
       </c>
       <c r="G712" t="n">
-        <v>22.7637462615967</v>
+        <v>22.763744354248</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>24.5</v>
       </c>
       <c r="G713" t="n">
-        <v>22.7637462615967</v>
+        <v>22.763744354248</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.4385452270508</v>
+        <v>22.4385471343994</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>22.2991809844971</v>
+        <v>22.2991790771484</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.2062644958496</v>
+        <v>22.2062664031982</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>21.8810653686523</v>
+        <v>21.8810691833496</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>24</v>
       </c>
       <c r="G720" t="n">
-        <v>22.2991809844971</v>
+        <v>22.2991790771484</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.5558700561523</v>
+        <v>21.5558738708496</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>22.1598072052002</v>
+        <v>22.1598091125488</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>21.9275245666504</v>
+        <v>21.927526473999</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24</v>
       </c>
       <c r="G724" t="n">
-        <v>22.2991809844971</v>
+        <v>22.2991790771484</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>23.088939666748</v>
+        <v>23.0889415740967</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>22.9031143188477</v>
+        <v>22.9031162261963</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>22.5779190063477</v>
+        <v>22.5779209136963</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24</v>
       </c>
       <c r="G728" t="n">
-        <v>22.2991809844971</v>
+        <v>22.2991790771484</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>22.9495697021484</v>
+        <v>22.9495716094971</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>24</v>
       </c>
       <c r="G732" t="n">
-        <v>22.2991809844971</v>
+        <v>22.2991790771484</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G733" t="n">
-        <v>22.252721786499</v>
+        <v>22.2527236938477</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>23</v>
       </c>
       <c r="G735" t="n">
-        <v>21.3700466156006</v>
+        <v>21.370044708252</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>22.5</v>
       </c>
       <c r="G737" t="n">
-        <v>20.9054794311523</v>
+        <v>20.905481338501</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>20.7196502685547</v>
+        <v>20.7196521759033</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>20.5802841186523</v>
+        <v>20.5802822113037</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>20.5802841186523</v>
+        <v>20.5802822113037</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G742" t="n">
-        <v>20.7196502685547</v>
+        <v>20.7196521759033</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G743" t="n">
-        <v>20.7196502685547</v>
+        <v>20.7196521759033</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>21.0913066864014</v>
+        <v>21.0913047790527</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G747" t="n">
-        <v>22.252721786499</v>
+        <v>22.2527236938477</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>21.9739818572998</v>
+        <v>21.9739837646484</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>21.8810653686523</v>
+        <v>21.8810691833496</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>23</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3700466156006</v>
+        <v>21.370044708252</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>21.4629611968994</v>
+        <v>21.4629592895508</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G752" t="n">
-        <v>21.6487865447998</v>
+        <v>21.6487846374512</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>21.2771320343018</v>
+        <v>21.2771339416504</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>21.6487865447998</v>
+        <v>21.6487846374512</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>21.6487865447998</v>
+        <v>21.6487846374512</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.4629611968994</v>
+        <v>21.4629592895508</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>23</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3700466156006</v>
+        <v>21.370044708252</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>21.0448474884033</v>
+        <v>21.044849395752</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>22.5</v>
       </c>
       <c r="G761" t="n">
-        <v>20.9054794311523</v>
+        <v>20.905481338501</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G763" t="n">
-        <v>21.5558700561523</v>
+        <v>21.5558738708496</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>23</v>
       </c>
       <c r="G764" t="n">
-        <v>21.3700466156006</v>
+        <v>21.370044708252</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>21.2771320343018</v>
+        <v>21.2771339416504</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G768" t="n">
-        <v>21.8810653686523</v>
+        <v>21.8810691833496</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G769" t="n">
-        <v>21.9275245666504</v>
+        <v>21.927526473999</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>22.1598072052002</v>
+        <v>22.1598091125488</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>22.1598072052002</v>
+        <v>22.1598091125488</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>22.4850063323975</v>
+        <v>22.4850044250488</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>22.9495697021484</v>
+        <v>22.9495716094971</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>25</v>
       </c>
       <c r="G775" t="n">
-        <v>23.2283096313477</v>
+        <v>23.2283115386963</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>23.3212223052979</v>
+        <v>23.3212242126465</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>23.3212223052979</v>
+        <v>23.3212242126465</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G779" t="n">
-        <v>23.3676776885986</v>
+        <v>23.3676815032959</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>25.25</v>
       </c>
       <c r="G780" t="n">
-        <v>23.4605960845947</v>
+        <v>23.4605941772461</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G782" t="n">
-        <v>23.9716186523438</v>
+        <v>23.9716167449951</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>25.75</v>
       </c>
       <c r="G784" t="n">
-        <v>23.9251594543457</v>
+        <v>23.9251613616943</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>24.2968158721924</v>
+        <v>24.2968139648438</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>24.2968158721924</v>
+        <v>24.2968139648438</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>24.2968158721924</v>
+        <v>24.2968139648438</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G789" t="n">
-        <v>24.3432712554932</v>
+        <v>24.3432693481445</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>24.2968158721924</v>
+        <v>24.2968139648438</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>26</v>
       </c>
       <c r="G791" t="n">
-        <v>24.1574440002441</v>
+        <v>24.1574420928955</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>24.2503566741943</v>
+        <v>24.250358581543</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G793" t="n">
-        <v>24.2968158721924</v>
+        <v>24.2968139648438</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>24.3432712554932</v>
+        <v>24.3432693481445</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3432712554932</v>
+        <v>24.3432693481445</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>26.5</v>
       </c>
       <c r="G797" t="n">
-        <v>24.6220092773438</v>
+        <v>24.6220111846924</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>27.5</v>
       </c>
       <c r="G799" t="n">
-        <v>25.5511436462402</v>
+        <v>25.5511417388916</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G801" t="n">
-        <v>25.7369709014893</v>
+        <v>25.736967086792</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>27.5</v>
       </c>
       <c r="G806" t="n">
-        <v>25.5511436462402</v>
+        <v>25.5511417388916</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>26.5731887817383</v>
+        <v>26.5731868743896</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>26.6196441650391</v>
+        <v>26.6196422576904</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>28.5</v>
       </c>
       <c r="G810" t="n">
-        <v>26.4802780151367</v>
+        <v>26.4802742004395</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>26.5731887817383</v>
+        <v>26.5731868743896</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>27.1306667327881</v>
+        <v>27.1306686401367</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>29</v>
       </c>
       <c r="G817" t="n">
-        <v>26.9448432922363</v>
+        <v>26.9448375701904</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>29</v>
       </c>
       <c r="G820" t="n">
-        <v>26.9448432922363</v>
+        <v>26.9448375701904</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>28.5</v>
       </c>
       <c r="G824" t="n">
-        <v>26.4802780151367</v>
+        <v>26.4802742004395</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>28.5</v>
       </c>
       <c r="G827" t="n">
-        <v>26.4802780151367</v>
+        <v>26.4802742004395</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>26.2944488525391</v>
+        <v>26.2944450378418</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>26.2944488525391</v>
+        <v>26.2944450378418</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>26.2944488525391</v>
+        <v>26.2944450378418</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>25.8298835754395</v>
+        <v>25.8298816680908</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>27.5</v>
       </c>
       <c r="G838" t="n">
-        <v>25.5511436462402</v>
+        <v>25.5511417388916</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>27.75</v>
       </c>
       <c r="G839" t="n">
-        <v>25.7834243774414</v>
+        <v>25.78342628479</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>25.6905097961426</v>
+        <v>25.6905117034912</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>25.6905097961426</v>
+        <v>25.6905117034912</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G843" t="n">
-        <v>25.6905097961426</v>
+        <v>25.6905117034912</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>27.75</v>
       </c>
       <c r="G846" t="n">
-        <v>25.7834243774414</v>
+        <v>25.78342628479</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>27</v>
       </c>
       <c r="G848" t="n">
-        <v>25.0865745544434</v>
+        <v>25.086576461792</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>24.6684665679932</v>
+        <v>24.6684646606445</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>24.5290966033936</v>
+        <v>24.5290946960449</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>26.5</v>
       </c>
       <c r="G853" t="n">
-        <v>24.6220092773438</v>
+        <v>24.6220111846924</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>26</v>
       </c>
       <c r="G856" t="n">
-        <v>24.1574440002441</v>
+        <v>24.1574420928955</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>26</v>
       </c>
       <c r="G857" t="n">
-        <v>24.1574440002441</v>
+        <v>24.1574420928955</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G859" t="n">
-        <v>24.1109867095947</v>
+        <v>24.1109886169434</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>27</v>
       </c>
       <c r="G860" t="n">
-        <v>25.0865745544434</v>
+        <v>25.086576461792</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>27</v>
       </c>
       <c r="G862" t="n">
-        <v>25.0865745544434</v>
+        <v>25.086576461792</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>26.5</v>
       </c>
       <c r="G866" t="n">
-        <v>24.6220092773438</v>
+        <v>24.6220111846924</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>26.5</v>
       </c>
       <c r="G867" t="n">
-        <v>24.6220092773438</v>
+        <v>24.6220111846924</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G868" t="n">
-        <v>24.5290966033936</v>
+        <v>24.5290946960449</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>26.5</v>
       </c>
       <c r="G869" t="n">
-        <v>24.6220092773438</v>
+        <v>24.6220111846924</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>24.8078384399414</v>
+        <v>24.8078346252441</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>27</v>
       </c>
       <c r="G872" t="n">
-        <v>25.0865745544434</v>
+        <v>25.086576461792</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>28</v>
       </c>
       <c r="G878" t="n">
-        <v>26.0157089233398</v>
+        <v>26.0157070159912</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>25.9692516326904</v>
+        <v>25.9692554473877</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>26.5267295837402</v>
+        <v>26.5267333984375</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>26.6196441650391</v>
+        <v>26.6196422576904</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>26.6661014556885</v>
+        <v>26.6661033630371</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>26.2944488525391</v>
+        <v>26.2944450378418</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>26.6661014556885</v>
+        <v>26.6661033630371</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G889" t="n">
-        <v>26.3873615264893</v>
+        <v>26.3873634338379</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>26.8054733276367</v>
+        <v>26.8054714202881</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>27.3164958953857</v>
+        <v>27.3164920806885</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>27.7346019744873</v>
+        <v>27.7346057891846</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>28.0133419036865</v>
+        <v>28.0133399963379</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>30.5</v>
       </c>
       <c r="G896" t="n">
-        <v>28.3385391235352</v>
+        <v>28.3385410308838</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>28.5243644714355</v>
+        <v>28.5243663787842</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>29.5464115142822</v>
+        <v>29.5464134216309</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>29.5464115142822</v>
+        <v>29.5464134216309</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>29.3605823516846</v>
+        <v>29.3605842590332</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>32.25</v>
       </c>
       <c r="G903" t="n">
-        <v>29.9645195007324</v>
+        <v>29.9645214080811</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>31.0794830322266</v>
+        <v>31.0794811248779</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G905" t="n">
-        <v>31.265308380127</v>
+        <v>31.2653064727783</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G906" t="n">
-        <v>32.0086059570312</v>
+        <v>32.0086097717285</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>33.0306587219238</v>
+        <v>33.0306625366211</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>32.8448371887207</v>
+        <v>32.8448295593262</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.1235694885254</v>
+        <v>33.1235733032227</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4487724304199</v>
+        <v>33.4487686157227</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G913" t="n">
-        <v>32.7983741760254</v>
+        <v>32.7983818054199</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G914" t="n">
-        <v>32.4267272949219</v>
+        <v>32.4267234802246</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.0306587219238</v>
+        <v>33.0306625366211</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G919" t="n">
-        <v>31.8692436218262</v>
+        <v>31.8692417144775</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G920" t="n">
-        <v>31.4975929260254</v>
+        <v>31.4975910186768</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>31.0330219268799</v>
+        <v>31.0330238342285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>30.9401111602783</v>
+        <v>30.9401054382324</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G923" t="n">
-        <v>31.0794830322266</v>
+        <v>31.0794811248779</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>30.4755420684814</v>
+        <v>30.4755439758301</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>30.6149139404297</v>
+        <v>30.6149120330811</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>30.2432613372803</v>
+        <v>30.2432632446289</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>32.5</v>
       </c>
       <c r="G928" t="n">
-        <v>30.1968059539795</v>
+        <v>30.1968078613281</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>30.8471965789795</v>
+        <v>30.8471946716309</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>30.5684604644775</v>
+        <v>30.5684585571289</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G931" t="n">
-        <v>30.9865665435791</v>
+        <v>30.9865646362305</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>32.75</v>
       </c>
       <c r="G932" t="n">
-        <v>30.4290885925293</v>
+        <v>30.4290866851807</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>30.7542839050293</v>
+        <v>30.7542819976807</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G934" t="n">
-        <v>30.5684604644775</v>
+        <v>30.5684585571289</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>30.7542839050293</v>
+        <v>30.7542819976807</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G937" t="n">
-        <v>31.4511299133301</v>
+        <v>31.4511280059814</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>34</v>
       </c>
       <c r="G938" t="n">
-        <v>31.5904998779297</v>
+        <v>31.5905075073242</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>34</v>
       </c>
       <c r="G939" t="n">
-        <v>31.5904998779297</v>
+        <v>31.5905075073242</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G941" t="n">
-        <v>33.541675567627</v>
+        <v>33.5416793823242</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G946" t="n">
-        <v>36.6542739868164</v>
+        <v>36.6542701721191</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>40</v>
       </c>
       <c r="G947" t="n">
-        <v>37.1652946472168</v>
+        <v>37.1652984619141</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G949" t="n">
-        <v>37.7128143310547</v>
+        <v>37.712818145752</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>39.5</v>
       </c>
       <c r="G951" t="n">
-        <v>37.2880172729492</v>
+        <v>37.288013458252</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>37.4296188354492</v>
+        <v>37.4296226501465</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>37.4768180847168</v>
+        <v>37.4768218994141</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>40.5</v>
       </c>
       <c r="G964" t="n">
-        <v>38.2320175170898</v>
+        <v>38.2320137023926</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G965" t="n">
-        <v>38.7984161376953</v>
+        <v>38.798412322998</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>40.5499992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>38.2792167663574</v>
+        <v>38.2792129516602</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>37.9488220214844</v>
+        <v>37.9488182067871</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>40.5</v>
       </c>
       <c r="G970" t="n">
-        <v>38.2320175170898</v>
+        <v>38.2320137023926</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G971" t="n">
-        <v>37.6184196472168</v>
+        <v>37.6184158325195</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G975" t="n">
-        <v>37.4296188354492</v>
+        <v>37.4296226501465</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>37.7128143310547</v>
+        <v>37.712818145752</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G979" t="n">
-        <v>37.9488220214844</v>
+        <v>37.9488182067871</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>38.0432205200195</v>
+        <v>38.0432167053223</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>40.5</v>
       </c>
       <c r="G986" t="n">
-        <v>38.2320175170898</v>
+        <v>38.2320137023926</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G987" t="n">
-        <v>38.8456192016602</v>
+        <v>38.8456153869629</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G988" t="n">
-        <v>38.6096229553223</v>
+        <v>38.6096267700195</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G989" t="n">
-        <v>38.6568183898926</v>
+        <v>38.6568222045898</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>40.2616233825684</v>
+        <v>40.2616195678711</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>41.3472213745117</v>
+        <v>41.3472175598145</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1006" t="n">
-        <v>42.8576240539551</v>
+        <v>42.8576202392578</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>43.0464172363281</v>
+        <v>43.0464210510254</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1011" t="n">
-        <v>42.8576240539551</v>
+        <v>42.8576202392578</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>48.5216217041016</v>
+        <v>48.5216255187988</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>52</v>
       </c>
       <c r="G1021" t="n">
-        <v>49.0880241394043</v>
+        <v>49.088020324707</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>51.5</v>
       </c>
       <c r="G1022" t="n">
-        <v>48.6160202026367</v>
+        <v>48.616024017334</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.7104263305664</v>
+        <v>48.7104225158691</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>49.9376258850098</v>
+        <v>49.9376220703125</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1028" t="n">
-        <v>52.0144233703613</v>
+        <v>52.0144271850586</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>55</v>
       </c>
       <c r="G1029" t="n">
-        <v>51.9200248718262</v>
+        <v>51.9200286865234</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G1031" t="n">
-        <v>51.1648254394531</v>
+        <v>51.1648216247559</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>54</v>
       </c>
       <c r="G1032" t="n">
-        <v>50.9760208129883</v>
+        <v>50.9760246276855</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>48.7104263305664</v>
+        <v>48.7104225158691</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>52</v>
       </c>
       <c r="G1035" t="n">
-        <v>49.0880241394043</v>
+        <v>49.088020324707</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1037" t="n">
-        <v>47.7664184570312</v>
+        <v>47.766414642334</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>50.5</v>
       </c>
       <c r="G1038" t="n">
-        <v>47.6720275878906</v>
+        <v>47.6720237731934</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G1041" t="n">
-        <v>50.6928253173828</v>
+        <v>50.6928215026855</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>49.1824226379395</v>
+        <v>49.1824188232422</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G1045" t="n">
-        <v>51.1648254394531</v>
+        <v>51.1648216247559</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>56.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>53.3360290527344</v>
+        <v>53.3360252380371</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>55</v>
       </c>
       <c r="G1049" t="n">
-        <v>51.9200248718262</v>
+        <v>51.9200286865234</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>54</v>
       </c>
       <c r="G1052" t="n">
-        <v>50.9760208129883</v>
+        <v>50.9760246276855</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>47</v>
       </c>
       <c r="G1060" t="n">
-        <v>44.3680229187012</v>
+        <v>44.3680152893066</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>45.5499992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>42.9992179870605</v>
+        <v>42.9992218017578</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1064" t="n">
-        <v>36.155216217041</v>
+        <v>36.1552200317383</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>35.116813659668</v>
+        <v>35.1168174743652</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1074" t="n">
-        <v>35.9192123413086</v>
+        <v>35.9192161560059</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>34.0784111022949</v>
+        <v>34.0784149169922</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>39.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>37.2880172729492</v>
+        <v>37.288013458252</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>36.155216217041</v>
+        <v>36.1552200317383</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>41</v>
       </c>
       <c r="G1086" t="n">
-        <v>38.7040138244629</v>
+        <v>38.7040176391602</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>42.25</v>
       </c>
       <c r="G1087" t="n">
-        <v>39.8840179443359</v>
+        <v>39.8840141296387</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>46.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>44.132022857666</v>
+        <v>44.1320266723633</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1095" t="n">
-        <v>44.7456283569336</v>
+        <v>44.7456245422363</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G1103" t="n">
-        <v>44.6984214782715</v>
+        <v>44.6984176635742</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>47</v>
       </c>
       <c r="G1105" t="n">
-        <v>44.3680229187012</v>
+        <v>44.3680152893066</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>43.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>41.3000221252441</v>
+        <v>41.3000183105469</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>41.3472213745117</v>
+        <v>41.3472175598145</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>46.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>44.132022857666</v>
+        <v>44.1320266723633</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>44.9344139099121</v>
+        <v>44.9344177246094</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1119" t="n">
-        <v>47.7664184570312</v>
+        <v>47.766414642334</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G1120" t="n">
-        <v>47.0584182739258</v>
+        <v>47.058422088623</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>51.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>48.6160202026367</v>
+        <v>48.616024017334</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>52</v>
       </c>
       <c r="G1124" t="n">
-        <v>49.0880241394043</v>
+        <v>49.088020324707</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1127" t="n">
-        <v>49.1824226379395</v>
+        <v>49.1824188232422</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>47.8608245849609</v>
+        <v>47.8608207702637</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1130" t="n">
-        <v>49.1824226379395</v>
+        <v>49.1824188232422</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>50.7872200012207</v>
+        <v>50.787223815918</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>51.0704231262207</v>
+        <v>51.0704193115234</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>55</v>
       </c>
       <c r="G1134" t="n">
-        <v>51.9200248718262</v>
+        <v>51.9200286865234</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G1137" t="n">
-        <v>51.0704231262207</v>
+        <v>51.0704193115234</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>50.7872200012207</v>
+        <v>50.787223815918</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G1140" t="n">
-        <v>50.5984191894531</v>
+        <v>50.5984153747559</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G1141" t="n">
-        <v>50.5984191894531</v>
+        <v>50.5984153747559</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1149" t="n">
-        <v>53.9024238586426</v>
+        <v>53.9024276733398</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>57.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>54.6576271057129</v>
+        <v>54.6576232910156</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1152" t="n">
-        <v>55.9792251586914</v>
+        <v>55.9792289733887</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>59.5</v>
       </c>
       <c r="G1153" t="n">
-        <v>56.1680297851562</v>
+        <v>56.168025970459</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>56.3568229675293</v>
+        <v>56.3568267822266</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>55.5072326660156</v>
+        <v>55.5072288513184</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>56.4512252807617</v>
+        <v>56.451229095459</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>61.5</v>
       </c>
       <c r="G1163" t="n">
-        <v>58.0560302734375</v>
+        <v>58.0560264587402</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G1164" t="n">
-        <v>60.5104293823242</v>
+        <v>60.510425567627</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>61.4544296264648</v>
+        <v>61.4544258117676</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1167" t="n">
-        <v>62.4928283691406</v>
+        <v>62.4928245544434</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1168" t="n">
-        <v>62.8704299926758</v>
+        <v>62.870433807373</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>66.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>62.7760238647461</v>
+        <v>62.7760276794434</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1170" t="n">
-        <v>63.4368324279785</v>
+        <v>63.436824798584</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>67.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>63.7200317382812</v>
+        <v>63.7200355529785</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>68.9000015258789</v>
       </c>
       <c r="G1172" t="n">
-        <v>65.041618347168</v>
+        <v>65.0416259765625</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>69.6999969482422</v>
       </c>
       <c r="G1173" t="n">
-        <v>65.7968215942383</v>
+        <v>65.7968292236328</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>68.3000030517578</v>
       </c>
       <c r="G1174" t="n">
-        <v>64.475227355957</v>
+        <v>64.4752349853516</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>69.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>65.6080322265625</v>
+        <v>65.608024597168</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1180" t="n">
-        <v>69.1008377075195</v>
+        <v>69.100830078125</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>72.3000030517578</v>
       </c>
       <c r="G1181" t="n">
-        <v>68.2512359619141</v>
+        <v>68.2512435913086</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>74.5</v>
       </c>
       <c r="G1182" t="n">
-        <v>70.3280334472656</v>
+        <v>70.3280410766602</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>75</v>
       </c>
       <c r="G1185" t="n">
-        <v>70.8000411987305</v>
+        <v>70.8000259399414</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>72.0999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>68.0624313354492</v>
+        <v>68.0624389648438</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G1190" t="n">
-        <v>69.0064392089844</v>
+        <v>69.0064315795898</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>75</v>
       </c>
       <c r="G1195" t="n">
-        <v>70.8000411987305</v>
+        <v>70.8000259399414</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>79.3000030517578</v>
       </c>
       <c r="G1198" t="n">
-        <v>74.8592376708984</v>
+        <v>74.859245300293</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>81.8000030517578</v>
       </c>
       <c r="G1203" t="n">
-        <v>77.2192459106445</v>
+        <v>77.2192535400391</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>85.1999969482422</v>
       </c>
       <c r="G1208" t="n">
-        <v>80.4288330078125</v>
+        <v>80.428825378418</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>84.0999984741211</v>
       </c>
       <c r="G1214" t="n">
-        <v>79.3904266357422</v>
+        <v>79.3904418945312</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>79.862434387207</v>
+        <v>79.8624267578125</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>86</v>
       </c>
       <c r="G1223" t="n">
-        <v>81.1840362548828</v>
+        <v>81.1840438842773</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>80.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>75.9920425415039</v>
+        <v>75.9920349121094</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>78.2576522827148</v>
+        <v>78.2576446533203</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>87.5</v>
       </c>
       <c r="G1233" t="n">
-        <v>82.6000442504883</v>
+        <v>82.6000366210938</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>85.8000030517578</v>
       </c>
       <c r="G1234" t="n">
-        <v>80.9952392578125</v>
+        <v>80.995246887207</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>85.1999969482422</v>
       </c>
       <c r="G1235" t="n">
-        <v>80.4288330078125</v>
+        <v>80.428825378418</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>86</v>
       </c>
       <c r="G1240" t="n">
-        <v>81.1840362548828</v>
+        <v>81.1840438842773</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>85.8000030517578</v>
       </c>
       <c r="G1242" t="n">
-        <v>80.9952392578125</v>
+        <v>80.995246887207</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>84.0999984741211</v>
       </c>
       <c r="G1243" t="n">
-        <v>79.3904266357422</v>
+        <v>79.3904418945312</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>84</v>
       </c>
       <c r="G1244" t="n">
-        <v>79.2960357666016</v>
+        <v>79.2960510253906</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>82.1999969482422</v>
       </c>
       <c r="G1246" t="n">
-        <v>77.5968322753906</v>
+        <v>77.5968246459961</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>82</v>
       </c>
       <c r="G1247" t="n">
-        <v>77.4080276489258</v>
+        <v>77.4080352783203</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>84</v>
       </c>
       <c r="G1250" t="n">
-        <v>79.2960357666016</v>
+        <v>79.2960510253906</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>88.5</v>
       </c>
       <c r="G1251" t="n">
-        <v>83.5440368652344</v>
+        <v>83.5440292358398</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>86.8000030517578</v>
       </c>
       <c r="G1253" t="n">
-        <v>81.9392395019531</v>
+        <v>81.9392318725586</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>91.0999984741211</v>
       </c>
       <c r="G1256" t="n">
-        <v>85.9984359741211</v>
+        <v>85.9984436035156</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>91.1999969482422</v>
       </c>
       <c r="G1257" t="n">
-        <v>86.0928344726562</v>
+        <v>86.0928421020508</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>95.5</v>
       </c>
       <c r="G1261" t="n">
-        <v>90.1520385742188</v>
+        <v>90.1520462036133</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>95.5</v>
       </c>
       <c r="G1262" t="n">
-        <v>90.1520385742188</v>
+        <v>90.1520462036133</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G1268" t="n">
-        <v>99.8752517700195</v>
+        <v>99.875244140625</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>103</v>
       </c>
       <c r="G1270" t="n">
-        <v>97.2320404052734</v>
+        <v>97.232048034668</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G1271" t="n">
-        <v>98.5536422729492</v>
+        <v>98.5536499023438</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>100.599998474121</v>
       </c>
       <c r="G1272" t="n">
-        <v>94.966438293457</v>
+        <v>94.9664459228516</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>100.599998474121</v>
       </c>
       <c r="G1273" t="n">
-        <v>94.966438293457</v>
+        <v>94.9664459228516</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>100</v>
       </c>
       <c r="G1274" t="n">
-        <v>94.4000473022461</v>
+        <v>94.4000396728516</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>98.5</v>
       </c>
       <c r="G1277" t="n">
-        <v>92.9840393066406</v>
+        <v>92.9840469360352</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G1278" t="n">
-        <v>93.1728439331055</v>
+        <v>93.1728363037109</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>95.7216491699219</v>
+        <v>95.7216415405273</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>98.4000015258789</v>
       </c>
       <c r="G1281" t="n">
-        <v>92.8896408081055</v>
+        <v>92.8896484375</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>98.3000030517578</v>
       </c>
       <c r="G1283" t="n">
-        <v>92.7952423095703</v>
+        <v>92.7952499389648</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>95.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>90.1520385742188</v>
+        <v>90.1520462036133</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G1293" t="n">
-        <v>95.7216491699219</v>
+        <v>95.7216415405273</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>103</v>
       </c>
       <c r="G1295" t="n">
-        <v>97.2320404052734</v>
+        <v>97.232048034668</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>112.199996948242</v>
       </c>
       <c r="G1300" t="n">
-        <v>105.916839599609</v>
+        <v>105.916854858398</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>100.81925201416</v>
+        <v>100.819259643555</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>104</v>
       </c>
       <c r="G1315" t="n">
-        <v>98.1760482788086</v>
+        <v>98.1760406494141</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G1316" t="n">
-        <v>98.3648452758789</v>
+        <v>98.3648376464844</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>108</v>
       </c>
       <c r="G1317" t="n">
-        <v>101.952041625977</v>
+        <v>101.952049255371</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>108.199996948242</v>
       </c>
       <c r="G1318" t="n">
-        <v>102.140846252441</v>
+        <v>102.140838623047</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>113.400001525879</v>
       </c>
       <c r="G1322" t="n">
-        <v>107.049644470215</v>
+        <v>107.04963684082</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G1328" t="n">
-        <v>101.574440002441</v>
+        <v>101.574447631836</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>108</v>
       </c>
       <c r="G1329" t="n">
-        <v>101.952041625977</v>
+        <v>101.952049255371</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>110.199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>104.028846740723</v>
+        <v>104.028854370117</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G1333" t="n">
-        <v>98.3648452758789</v>
+        <v>98.3648376464844</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>108</v>
       </c>
       <c r="G1336" t="n">
-        <v>101.952041625977</v>
+        <v>101.952049255371</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>111.199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>104.972854614258</v>
+        <v>104.972846984863</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>114</v>
       </c>
       <c r="G1341" t="n">
-        <v>107.616050720215</v>
+        <v>107.616058349609</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>115.800003051758</v>
       </c>
       <c r="G1342" t="n">
-        <v>109.315254211426</v>
+        <v>109.315246582031</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>115.400001525879</v>
       </c>
       <c r="G1353" t="n">
-        <v>108.937652587891</v>
+        <v>108.937660217285</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>117.400001525879</v>
       </c>
       <c r="G1356" t="n">
-        <v>110.825653076172</v>
+        <v>110.825660705566</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>119.599998474121</v>
       </c>
       <c r="G1357" t="n">
-        <v>112.902450561523</v>
+        <v>112.902458190918</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>118.400001525879</v>
       </c>
       <c r="G1358" t="n">
-        <v>111.769660949707</v>
+        <v>111.769653320312</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>120.199996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>113.468849182129</v>
+        <v>113.468841552734</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>120.800003051758</v>
       </c>
       <c r="G1362" t="n">
-        <v>114.035263061523</v>
+        <v>114.035255432129</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G1363" t="n">
-        <v>113.657653808594</v>
+        <v>113.657646179199</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>121.400001525879</v>
       </c>
       <c r="G1366" t="n">
-        <v>114.601654052734</v>
+        <v>114.601661682129</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G1371" t="n">
-        <v>118.566444396973</v>
+        <v>118.566452026367</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>133</v>
       </c>
       <c r="G1376" t="n">
-        <v>125.552047729492</v>
+        <v>125.552055358887</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>133.199996948242</v>
       </c>
       <c r="G1377" t="n">
-        <v>125.740859985352</v>
+        <v>125.740867614746</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>133</v>
       </c>
       <c r="G1378" t="n">
-        <v>125.552047729492</v>
+        <v>125.552055358887</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>138</v>
       </c>
       <c r="G1380" t="n">
-        <v>130.272048950195</v>
+        <v>130.272064208984</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>138</v>
       </c>
       <c r="G1381" t="n">
-        <v>130.272048950195</v>
+        <v>130.272064208984</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>138</v>
       </c>
       <c r="G1382" t="n">
-        <v>130.272048950195</v>
+        <v>130.272064208984</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G1383" t="n">
-        <v>132.348846435547</v>
+        <v>132.348861694336</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>143.600006103516</v>
       </c>
       <c r="G1389" t="n">
-        <v>135.558486938477</v>
+        <v>135.558471679688</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G1391" t="n">
-        <v>130.083236694336</v>
+        <v>130.083251953125</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>142.399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>134.425659179688</v>
+        <v>134.425643920898</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>144.399993896484</v>
       </c>
       <c r="G1398" t="n">
-        <v>136.31364440918</v>
+        <v>136.313659667969</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G1400" t="n">
-        <v>136.691253662109</v>
+        <v>136.691268920898</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G1401" t="n">
-        <v>138.012878417969</v>
+        <v>138.01286315918</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>143.600006103516</v>
       </c>
       <c r="G1403" t="n">
-        <v>135.558486938477</v>
+        <v>135.558471679688</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>145</v>
       </c>
       <c r="G1404" t="n">
-        <v>136.88005065918</v>
+        <v>136.880065917969</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G1406" t="n">
-        <v>138.012878417969</v>
+        <v>138.01286315918</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>144.199996948242</v>
       </c>
       <c r="G1407" t="n">
-        <v>136.124862670898</v>
+        <v>136.124877929688</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>142.399993896484</v>
       </c>
       <c r="G1408" t="n">
-        <v>134.425659179688</v>
+        <v>134.425643920898</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>148.600006103516</v>
       </c>
       <c r="G1415" t="n">
-        <v>140.278472900391</v>
+        <v>140.27848815918</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>150.199996948242</v>
       </c>
       <c r="G1416" t="n">
-        <v>141.788879394531</v>
+        <v>141.788848876953</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>148.600006103516</v>
       </c>
       <c r="G1417" t="n">
-        <v>140.278472900391</v>
+        <v>140.27848815918</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>150.199996948242</v>
       </c>
       <c r="G1418" t="n">
-        <v>141.788879394531</v>
+        <v>141.788848876953</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>151.800003051758</v>
       </c>
       <c r="G1421" t="n">
-        <v>143.299285888672</v>
+        <v>143.299270629883</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>154.600006103516</v>
       </c>
       <c r="G1422" t="n">
-        <v>145.942474365234</v>
+        <v>145.942459106445</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>152.199996948242</v>
       </c>
       <c r="G1423" t="n">
-        <v>143.676849365234</v>
+        <v>143.676864624023</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G1426" t="n">
-        <v>148.963256835938</v>
+        <v>148.963272094727</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>158</v>
       </c>
       <c r="G1432" t="n">
-        <v>149.152069091797</v>
+        <v>149.152053833008</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>165</v>
       </c>
       <c r="G1434" t="n">
-        <v>155.760070800781</v>
+        <v>155.760055541992</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>165.800003051758</v>
       </c>
       <c r="G1436" t="n">
-        <v>156.51530456543</v>
+        <v>156.515289306641</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>165.800003051758</v>
       </c>
       <c r="G1437" t="n">
-        <v>156.51530456543</v>
+        <v>156.515289306641</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>168.600006103516</v>
       </c>
       <c r="G1439" t="n">
-        <v>159.158493041992</v>
+        <v>159.158477783203</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>181.600006103516</v>
       </c>
       <c r="G1444" t="n">
-        <v>171.43049621582</v>
+        <v>171.430480957031</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>175.600006103516</v>
       </c>
       <c r="G1447" t="n">
-        <v>165.766479492188</v>
+        <v>165.766494750977</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>168</v>
       </c>
       <c r="G1449" t="n">
-        <v>158.592071533203</v>
+        <v>158.592102050781</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>168.399993896484</v>
       </c>
       <c r="G1454" t="n">
-        <v>159.747375488281</v>
+        <v>159.747360229492</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>167.800003051758</v>
       </c>
       <c r="G1455" t="n">
-        <v>159.178192138672</v>
+        <v>159.178207397461</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>167.800003051758</v>
       </c>
       <c r="G1456" t="n">
-        <v>159.178192138672</v>
+        <v>159.178207397461</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>167</v>
       </c>
       <c r="G1457" t="n">
-        <v>158.419311523438</v>
+        <v>158.419296264648</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>165.399993896484</v>
       </c>
       <c r="G1458" t="n">
-        <v>156.901504516602</v>
+        <v>156.901519775391</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>151.399993896484</v>
       </c>
       <c r="G1460" t="n">
-        <v>143.620849609375</v>
+        <v>143.620834350586</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1461" t="n">
-        <v>145.328369140625</v>
+        <v>145.328353881836</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G1465" t="n">
-        <v>149.692001342773</v>
+        <v>149.692016601562</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G1470" t="n">
-        <v>152.348159790039</v>
+        <v>152.34814453125</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>167.199996948242</v>
       </c>
       <c r="G1471" t="n">
-        <v>158.609024047852</v>
+        <v>158.609008789062</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>173</v>
       </c>
       <c r="G1472" t="n">
-        <v>164.11100769043</v>
+        <v>164.111022949219</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>167</v>
       </c>
       <c r="G1485" t="n">
-        <v>158.419311523438</v>
+        <v>158.419296264648</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>188</v>
       </c>
       <c r="G1490" t="n">
-        <v>178.340286254883</v>
+        <v>178.340270996094</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>189</v>
       </c>
       <c r="G1493" t="n">
-        <v>179.288909912109</v>
+        <v>179.288925170898</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>188</v>
       </c>
       <c r="G1497" t="n">
-        <v>178.340286254883</v>
+        <v>178.340270996094</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>175</v>
       </c>
       <c r="G1500" t="n">
-        <v>166.008255004883</v>
+        <v>166.008239746094</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>182</v>
       </c>
       <c r="G1510" t="n">
-        <v>172.648590087891</v>
+        <v>172.648574829102</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>182</v>
       </c>
       <c r="G1512" t="n">
-        <v>172.648590087891</v>
+        <v>172.648574829102</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>179</v>
       </c>
       <c r="G1513" t="n">
-        <v>169.802734375</v>
+        <v>169.802719116211</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>173</v>
       </c>
       <c r="G1516" t="n">
-        <v>164.11100769043</v>
+        <v>164.111022949219</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>170.800003051758</v>
       </c>
       <c r="G1522" t="n">
-        <v>162.024047851562</v>
+        <v>162.024063110352</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>173.199996948242</v>
       </c>
       <c r="G1523" t="n">
-        <v>164.300720214844</v>
+        <v>164.300735473633</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>175</v>
       </c>
       <c r="G1524" t="n">
-        <v>166.008255004883</v>
+        <v>166.008239746094</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G1532" t="n">
-        <v>149.122833251953</v>
+        <v>149.122848510742</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>164.800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>156.332336425781</v>
+        <v>156.33235168457</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>162.399993896484</v>
       </c>
       <c r="G1539" t="n">
-        <v>154.055648803711</v>
+        <v>154.0556640625</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>167.199996948242</v>
       </c>
       <c r="G1549" t="n">
-        <v>158.609024047852</v>
+        <v>158.609008789062</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>144.199996948242</v>
       </c>
       <c r="G1554" t="n">
-        <v>136.790802001953</v>
+        <v>136.790817260742</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>138</v>
       </c>
       <c r="G1555" t="n">
-        <v>130.90934753418</v>
+        <v>130.909362792969</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>138</v>
       </c>
       <c r="G1559" t="n">
-        <v>130.90934753418</v>
+        <v>130.909362792969</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>134.800003051758</v>
       </c>
       <c r="G1563" t="n">
-        <v>127.873802185059</v>
+        <v>127.873794555664</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G1565" t="n">
-        <v>131.099090576172</v>
+        <v>131.099075317383</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>144</v>
       </c>
       <c r="G1569" t="n">
-        <v>136.601089477539</v>
+        <v>136.60107421875</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>141</v>
       </c>
       <c r="G1570" t="n">
-        <v>133.755218505859</v>
+        <v>133.75520324707</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>123.400001525879</v>
       </c>
       <c r="G1573" t="n">
-        <v>117.059524536133</v>
+        <v>117.059532165527</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>130.600006103516</v>
       </c>
       <c r="G1574" t="n">
-        <v>123.889587402344</v>
+        <v>123.889595031738</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>130.199996948242</v>
       </c>
       <c r="G1575" t="n">
-        <v>123.510139465332</v>
+        <v>123.510131835938</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>144</v>
       </c>
       <c r="G1577" t="n">
-        <v>136.601089477539</v>
+        <v>136.60107421875</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>144.399993896484</v>
       </c>
       <c r="G1580" t="n">
-        <v>136.980499267578</v>
+        <v>136.980514526367</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G1586" t="n">
-        <v>143.810592651367</v>
+        <v>143.810577392578</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G1588" t="n">
-        <v>146.276992797852</v>
+        <v>146.276977539062</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>149</v>
       </c>
       <c r="G1590" t="n">
-        <v>141.344177246094</v>
+        <v>141.344161987305</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>148.300003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>140.680145263672</v>
+        <v>140.680160522461</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G1599" t="n">
-        <v>137.359970092773</v>
+        <v>137.359954833984</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>148.899993896484</v>
       </c>
       <c r="G1602" t="n">
-        <v>141.249298095703</v>
+        <v>141.249282836914</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>134.699996948242</v>
       </c>
       <c r="G1607" t="n">
-        <v>127.778907775879</v>
+        <v>127.778915405273</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>126.545715332031</v>
+        <v>126.545707702637</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>135.5</v>
       </c>
       <c r="G1611" t="n">
-        <v>128.537811279297</v>
+        <v>128.537826538086</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>129.199996948242</v>
       </c>
       <c r="G1612" t="n">
-        <v>122.561515808105</v>
+        <v>122.5615234375</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G1616" t="n">
-        <v>112.031845092773</v>
+        <v>112.031852722168</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G1621" t="n">
-        <v>120.664276123047</v>
+        <v>120.664283752441</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>124</v>
       </c>
       <c r="G1624" t="n">
-        <v>117.628692626953</v>
+        <v>117.628700256348</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>125.300003051758</v>
       </c>
       <c r="G1625" t="n">
-        <v>118.86190032959</v>
+        <v>118.861907958984</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>126.599998474121</v>
       </c>
       <c r="G1629" t="n">
-        <v>120.095100402832</v>
+        <v>120.095108032227</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>129</v>
       </c>
       <c r="G1633" t="n">
-        <v>122.371795654297</v>
+        <v>122.371788024902</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>129.300003051758</v>
       </c>
       <c r="G1634" t="n">
-        <v>122.656372070312</v>
+        <v>122.656379699707</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>133.100006103516</v>
       </c>
       <c r="G1635" t="n">
-        <v>126.261131286621</v>
+        <v>126.261138916016</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G1637" t="n">
-        <v>125.976547241211</v>
+        <v>125.976539611816</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>123.400001525879</v>
       </c>
       <c r="G1639" t="n">
-        <v>117.059524536133</v>
+        <v>117.059532165527</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>112.69588470459</v>
+        <v>112.695892333984</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>115.5</v>
       </c>
       <c r="G1643" t="n">
-        <v>109.565437316895</v>
+        <v>109.565444946289</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G1648" t="n">
-        <v>113.644515991211</v>
+        <v>113.644508361816</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G1654" t="n">
-        <v>113.739364624023</v>
+        <v>113.739356994629</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>128</v>
       </c>
       <c r="G1658" t="n">
-        <v>121.42317199707</v>
+        <v>121.423179626465</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>130.399993896484</v>
       </c>
       <c r="G1659" t="n">
-        <v>123.699851989746</v>
+        <v>123.699859619141</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>124.5</v>
       </c>
       <c r="G1662" t="n">
-        <v>118.103004455566</v>
+        <v>118.103012084961</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>130.399993896484</v>
       </c>
       <c r="G1665" t="n">
-        <v>123.699851989746</v>
+        <v>123.699859619141</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>134.100006103516</v>
       </c>
       <c r="G1668" t="n">
-        <v>127.209732055664</v>
+        <v>127.209739685059</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>135.899993896484</v>
       </c>
       <c r="G1670" t="n">
-        <v>128.917266845703</v>
+        <v>128.917251586914</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>131.899993896484</v>
       </c>
       <c r="G1671" t="n">
-        <v>125.122764587402</v>
+        <v>125.122772216797</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G1673" t="n">
-        <v>126.735427856445</v>
+        <v>126.73543548584</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>134.800003051758</v>
       </c>
       <c r="G1675" t="n">
-        <v>127.873802185059</v>
+        <v>127.873794555664</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1676" t="n">
-        <v>126.545715332031</v>
+        <v>126.545707702637</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>134.199996948242</v>
       </c>
       <c r="G1677" t="n">
-        <v>127.304611206055</v>
+        <v>127.304618835449</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G1685" t="n">
-        <v>125.027923583984</v>
+        <v>125.027931213379</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>129.199996948242</v>
       </c>
       <c r="G1686" t="n">
-        <v>122.561515808105</v>
+        <v>122.5615234375</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>129.199996948242</v>
       </c>
       <c r="G1687" t="n">
-        <v>122.561515808105</v>
+        <v>122.5615234375</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>126.300003051758</v>
       </c>
       <c r="G1688" t="n">
-        <v>119.810531616211</v>
+        <v>119.810523986816</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>123.699996948242</v>
       </c>
       <c r="G1690" t="n">
-        <v>117.344116210938</v>
+        <v>117.344108581543</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>122.199996948242</v>
       </c>
       <c r="G1696" t="n">
-        <v>115.921188354492</v>
+        <v>115.921180725098</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>120.900001525879</v>
       </c>
       <c r="G1699" t="n">
-        <v>114.687995910645</v>
+        <v>114.68798828125</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G1700" t="n">
-        <v>112.69588470459</v>
+        <v>112.695892333984</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>107</v>
       </c>
       <c r="G1713" t="n">
-        <v>102.291061401367</v>
+        <v>102.291053771973</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G1717" t="n">
-        <v>100.665878295898</v>
+        <v>100.665885925293</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>116.800003051758</v>
       </c>
       <c r="G1720" t="n">
-        <v>111.659774780273</v>
+        <v>111.659782409668</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G1723" t="n">
-        <v>105.828231811523</v>
+        <v>105.828224182129</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>108.199996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>103.438255310059</v>
+        <v>103.438247680664</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>108</v>
       </c>
       <c r="G1725" t="n">
-        <v>103.247047424316</v>
+        <v>103.247055053711</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>107.400001525879</v>
       </c>
       <c r="G1729" t="n">
-        <v>102.673461914062</v>
+        <v>102.673454284668</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G1731" t="n">
-        <v>104.967842102051</v>
+        <v>104.967849731445</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G1733" t="n">
-        <v>105.828231811523</v>
+        <v>105.828224182129</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G1735" t="n">
-        <v>114.623359680176</v>
+        <v>114.623352050781</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>109.699996948242</v>
       </c>
       <c r="G1739" t="n">
-        <v>104.872230529785</v>
+        <v>104.87223815918</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>104.099998474121</v>
       </c>
       <c r="G1742" t="n">
-        <v>99.518684387207</v>
+        <v>99.5186767578125</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>118.400001525879</v>
       </c>
       <c r="G1752" t="n">
-        <v>113.189353942871</v>
+        <v>113.189361572266</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G1756" t="n">
-        <v>113.667366027832</v>
+        <v>113.667358398438</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G1757" t="n">
-        <v>115.388130187988</v>
+        <v>115.388137817383</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>113.667366027832</v>
+        <v>113.667358398438</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1767" t="n">
-        <v>111.181777954102</v>
+        <v>111.181785583496</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>116.199996948242</v>
       </c>
       <c r="G1769" t="n">
-        <v>111.08617401123</v>
+        <v>111.086181640625</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G1770" t="n">
-        <v>113.667366027832</v>
+        <v>113.667358398438</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>113.400001525879</v>
       </c>
       <c r="G1779" t="n">
-        <v>108.409408569336</v>
+        <v>108.409400939941</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1780" t="n">
-        <v>109.74779510498</v>
+        <v>109.747787475586</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>116</v>
       </c>
       <c r="G1782" t="n">
-        <v>110.894981384277</v>
+        <v>110.894973754883</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>116.800003051758</v>
       </c>
       <c r="G1783" t="n">
-        <v>111.659774780273</v>
+        <v>111.659782409668</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>121.699996948242</v>
       </c>
       <c r="G1788" t="n">
-        <v>116.344123840332</v>
+        <v>116.344131469727</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G1789" t="n">
-        <v>114.623359680176</v>
+        <v>114.623352050781</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>121</v>
       </c>
       <c r="G1790" t="n">
-        <v>115.674942016602</v>
+        <v>115.674934387207</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>121.099998474121</v>
       </c>
       <c r="G1791" t="n">
-        <v>115.770538330078</v>
+        <v>115.770530700684</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>125</v>
       </c>
       <c r="G1793" t="n">
-        <v>119.498901367188</v>
+        <v>119.498908996582</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>124</v>
       </c>
       <c r="G1797" t="n">
-        <v>118.542907714844</v>
+        <v>118.542915344238</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G1802" t="n">
-        <v>121.602081298828</v>
+        <v>121.602088928223</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G1804" t="n">
-        <v>119.116508483887</v>
+        <v>119.116516113281</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>136.199996948242</v>
       </c>
       <c r="G1806" t="n">
-        <v>130.205993652344</v>
+        <v>130.206008911133</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G1807" t="n">
-        <v>130.110412597656</v>
+        <v>130.110427856445</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>136.399993896484</v>
       </c>
       <c r="G1808" t="n">
-        <v>130.397186279297</v>
+        <v>130.397201538086</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>132.699996948242</v>
       </c>
       <c r="G1810" t="n">
-        <v>126.860023498535</v>
+        <v>126.86003112793</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>129.699996948242</v>
       </c>
       <c r="G1813" t="n">
-        <v>123.992073059082</v>
+        <v>123.992065429688</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>130.899993896484</v>
       </c>
       <c r="G1814" t="n">
-        <v>125.139251708984</v>
+        <v>125.13924407959</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G1822" t="n">
-        <v>118.63850402832</v>
+        <v>118.638511657715</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>124.199996948242</v>
       </c>
       <c r="G1823" t="n">
-        <v>118.734115600586</v>
+        <v>118.734107971191</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G1825" t="n">
-        <v>115.388130187988</v>
+        <v>115.388137817383</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>119.5</v>
       </c>
       <c r="G1828" t="n">
-        <v>114.240951538086</v>
+        <v>114.24095916748</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>117.5</v>
       </c>
       <c r="G1829" t="n">
-        <v>112.328971862793</v>
+        <v>112.328979492188</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G1830" t="n">
-        <v>112.42456817627</v>
+        <v>112.424575805664</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1831" t="n">
-        <v>111.564178466797</v>
+        <v>111.564170837402</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1836" t="n">
-        <v>111.181777954102</v>
+        <v>111.181785583496</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G1838" t="n">
-        <v>110.03458404541</v>
+        <v>110.034591674805</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>117.800003051758</v>
       </c>
       <c r="G1842" t="n">
-        <v>112.615776062012</v>
+        <v>112.615768432617</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>120</v>
       </c>
       <c r="G1845" t="n">
-        <v>114.718955993652</v>
+        <v>114.718948364258</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>122.900001525879</v>
       </c>
       <c r="G1847" t="n">
-        <v>117.491325378418</v>
+        <v>117.491333007812</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>116.199996948242</v>
       </c>
       <c r="G1857" t="n">
-        <v>111.08617401123</v>
+        <v>111.086181640625</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>116</v>
       </c>
       <c r="G1858" t="n">
-        <v>110.894981384277</v>
+        <v>110.894973754883</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>114.5</v>
       </c>
       <c r="G1859" t="n">
-        <v>109.461006164551</v>
+        <v>109.460998535156</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>111</v>
       </c>
       <c r="G1869" t="n">
-        <v>106.115020751953</v>
+        <v>106.115028381348</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G1870" t="n">
-        <v>105.828231811523</v>
+        <v>105.828224182129</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>108.199996948242</v>
       </c>
       <c r="G1873" t="n">
-        <v>103.438255310059</v>
+        <v>103.438247680664</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>106.900001525879</v>
       </c>
       <c r="G1877" t="n">
-        <v>102.195457458496</v>
+        <v>102.195465087891</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>106.900001525879</v>
       </c>
       <c r="G1878" t="n">
-        <v>102.195457458496</v>
+        <v>102.195465087891</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>106.5</v>
       </c>
       <c r="G1881" t="n">
-        <v>101.813064575195</v>
+        <v>101.81307220459</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>106.400001525879</v>
       </c>
       <c r="G1886" t="n">
-        <v>101.717460632324</v>
+        <v>101.717468261719</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>118.400001525879</v>
       </c>
       <c r="G1898" t="n">
-        <v>113.189353942871</v>
+        <v>113.189361572266</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1902" t="n">
-        <v>109.269798278809</v>
+        <v>109.269805908203</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1903" t="n">
-        <v>109.74779510498</v>
+        <v>109.747787475586</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1910" t="n">
-        <v>109.269798278809</v>
+        <v>109.269805908203</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1911" t="n">
-        <v>109.74779510498</v>
+        <v>109.747787475586</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>113</v>
       </c>
       <c r="G1913" t="n">
-        <v>108.027008056641</v>
+        <v>108.027015686035</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>113</v>
       </c>
       <c r="G1915" t="n">
-        <v>108.027008056641</v>
+        <v>108.027015686035</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1917" t="n">
-        <v>109.269798278809</v>
+        <v>109.269805908203</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G1936" t="n">
-        <v>98.6582946777344</v>
+        <v>98.6583023071289</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>102.599998474121</v>
       </c>
       <c r="G1937" t="n">
-        <v>98.0846939086914</v>
+        <v>98.0847015380859</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G1941" t="n">
-        <v>100.283485412598</v>
+        <v>100.283477783203</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G1946" t="n">
-        <v>98.6582946777344</v>
+        <v>98.6583023071289</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>107</v>
       </c>
       <c r="G1954" t="n">
-        <v>102.291061401367</v>
+        <v>102.291053771973</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>105</v>
       </c>
       <c r="G1956" t="n">
-        <v>100.379081726074</v>
+        <v>100.37907409668</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>103</v>
       </c>
       <c r="G1957" t="n">
-        <v>98.4671020507812</v>
+        <v>98.4670944213867</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>102.599998474121</v>
       </c>
       <c r="G1958" t="n">
-        <v>98.0846939086914</v>
+        <v>98.0847015380859</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>101.5</v>
       </c>
       <c r="G1960" t="n">
-        <v>97.0331039428711</v>
+        <v>97.0331115722656</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G1962" t="n">
-        <v>96.3639297485352</v>
+        <v>96.3639221191406</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G1965" t="n">
-        <v>97.2869567871094</v>
+        <v>97.2869491577148</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G1967" t="n">
-        <v>97.2869567871094</v>
+        <v>97.2869491577148</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G1968" t="n">
-        <v>97.2869567871094</v>
+        <v>97.2869491577148</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>96.1500015258789</v>
       </c>
       <c r="G1970" t="n">
-        <v>92.7990112304688</v>
+        <v>92.7990036010742</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>97.9000015258789</v>
       </c>
       <c r="G1976" t="n">
-        <v>94.4880142211914</v>
+        <v>94.4880218505859</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>94.6500015258789</v>
       </c>
       <c r="G1978" t="n">
-        <v>91.3512878417969</v>
+        <v>91.3512802124023</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>96.6500015258789</v>
       </c>
       <c r="G1980" t="n">
-        <v>93.2815780639648</v>
+        <v>93.2815856933594</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>96.6500015258789</v>
       </c>
       <c r="G1981" t="n">
-        <v>93.2815780639648</v>
+        <v>93.2815856933594</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>98.6500015258789</v>
       </c>
       <c r="G1982" t="n">
-        <v>95.2118835449219</v>
+        <v>95.2118759155273</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>95.8000030517578</v>
       </c>
       <c r="G1983" t="n">
-        <v>92.4612121582031</v>
+        <v>92.4612045288086</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>93.3000030517578</v>
       </c>
       <c r="G1991" t="n">
-        <v>90.04833984375</v>
+        <v>90.0483322143555</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>93.9499969482422</v>
       </c>
       <c r="G1994" t="n">
-        <v>90.6756744384766</v>
+        <v>90.6756820678711</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>99.8499984741211</v>
       </c>
       <c r="G1999" t="n">
-        <v>96.3700561523438</v>
+        <v>96.3700485229492</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G2002" t="n">
-        <v>100.568450927734</v>
+        <v>100.56844329834</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G2007" t="n">
-        <v>99.1207275390625</v>
+        <v>99.120719909668</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G2008" t="n">
-        <v>99.7963333129883</v>
+        <v>99.7963256835938</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G2009" t="n">
-        <v>102.112686157227</v>
+        <v>102.112693786621</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>106</v>
       </c>
       <c r="G2010" t="n">
-        <v>102.305717468262</v>
+        <v>102.305709838867</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G2017" t="n">
-        <v>102.112686157227</v>
+        <v>102.112693786621</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G2020" t="n">
-        <v>99.7963333129883</v>
+        <v>99.7963256835938</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G2021" t="n">
-        <v>101.63011932373</v>
+        <v>101.630111694336</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>114</v>
       </c>
       <c r="G2027" t="n">
-        <v>110.026901245117</v>
+        <v>110.026893615723</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>121</v>
       </c>
       <c r="G2032" t="n">
-        <v>116.782936096191</v>
+        <v>116.782943725586</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>121.900001525879</v>
       </c>
       <c r="G2033" t="n">
-        <v>117.651573181152</v>
+        <v>117.651580810547</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>123</v>
       </c>
       <c r="G2034" t="n">
-        <v>118.713241577148</v>
+        <v>118.713233947754</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>123</v>
       </c>
       <c r="G2035" t="n">
-        <v>118.713241577148</v>
+        <v>118.713233947754</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>123</v>
       </c>
       <c r="G2036" t="n">
-        <v>118.713241577148</v>
+        <v>118.713233947754</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G2037" t="n">
-        <v>116.493392944336</v>
+        <v>116.493385314941</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>114.400001525879</v>
       </c>
       <c r="G2043" t="n">
-        <v>110.412956237793</v>
+        <v>110.412963867188</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>116.599998474121</v>
       </c>
       <c r="G2046" t="n">
-        <v>112.536293029785</v>
+        <v>112.536285400391</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G2048" t="n">
-        <v>111.281593322754</v>
+        <v>111.281600952148</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G2049" t="n">
-        <v>111.281593322754</v>
+        <v>111.281600952148</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>124.699996948242</v>
       </c>
       <c r="G2054" t="n">
-        <v>120.353981018066</v>
+        <v>120.353988647461</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>125.300003051758</v>
       </c>
       <c r="G2056" t="n">
-        <v>120.933074951172</v>
+        <v>120.933082580566</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>126.099998474121</v>
       </c>
       <c r="G2058" t="n">
-        <v>121.705192565918</v>
+        <v>121.705184936523</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2064" t="n">
-        <v>118.423683166504</v>
+        <v>118.423690795898</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>120</v>
       </c>
       <c r="G2068" t="n">
-        <v>115.817794799805</v>
+        <v>115.81778717041</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>118.5</v>
       </c>
       <c r="G2069" t="n">
-        <v>114.370079040527</v>
+        <v>114.370071411133</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>117.099998474121</v>
       </c>
       <c r="G2072" t="n">
-        <v>113.018852233887</v>
+        <v>113.018859863281</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>117.099998474121</v>
       </c>
       <c r="G2073" t="n">
-        <v>113.018852233887</v>
+        <v>113.018859863281</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>117.800003051758</v>
       </c>
       <c r="G2074" t="n">
-        <v>113.694458007812</v>
+        <v>113.694465637207</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>117.800003051758</v>
       </c>
       <c r="G2076" t="n">
-        <v>113.694458007812</v>
+        <v>113.694465637207</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>118.400001525879</v>
       </c>
       <c r="G2077" t="n">
-        <v>114.273551940918</v>
+        <v>114.273559570312</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>115.400001525879</v>
       </c>
       <c r="G2080" t="n">
-        <v>111.378112792969</v>
+        <v>111.378105163574</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>113.400001525879</v>
       </c>
       <c r="G2082" t="n">
-        <v>109.447807312012</v>
+        <v>109.447814941406</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>112.5</v>
       </c>
       <c r="G2086" t="n">
-        <v>108.579177856445</v>
+        <v>108.57918548584</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>105</v>
       </c>
       <c r="G2089" t="n">
-        <v>101.340560913086</v>
+        <v>101.34056854248</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G2092" t="n">
-        <v>97.2869567871094</v>
+        <v>97.2869491577148</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>99.3000030517578</v>
       </c>
       <c r="G2093" t="n">
-        <v>95.839225769043</v>
+        <v>95.8392181396484</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>101.5</v>
       </c>
       <c r="G2095" t="n">
-        <v>97.9625549316406</v>
+        <v>97.9625473022461</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G2097" t="n">
-        <v>97.8660278320312</v>
+        <v>97.8660354614258</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>101.5</v>
       </c>
       <c r="G2100" t="n">
-        <v>97.9625549316406</v>
+        <v>97.9625473022461</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G2101" t="n">
-        <v>97.8660278320312</v>
+        <v>97.8660354614258</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G2105" t="n">
-        <v>97.2869567871094</v>
+        <v>97.2869491577148</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>100.5</v>
       </c>
       <c r="G2108" t="n">
-        <v>96.9973983764648</v>
+        <v>96.9974060058594</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>98.75</v>
       </c>
       <c r="G2115" t="n">
-        <v>95.3083953857422</v>
+        <v>95.3083877563477</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2117" t="n">
-        <v>93.329833984375</v>
+        <v>93.3298263549805</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>97.9499969482422</v>
       </c>
       <c r="G2120" t="n">
-        <v>94.5362777709961</v>
+        <v>94.5362701416016</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>98.9000015258789</v>
       </c>
       <c r="G2123" t="n">
-        <v>95.4531707763672</v>
+        <v>95.4531631469727</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>101.5</v>
       </c>
       <c r="G2127" t="n">
-        <v>97.9625549316406</v>
+        <v>97.9625473022461</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G2129" t="n">
-        <v>100.568450927734</v>
+        <v>100.56844329834</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>105</v>
       </c>
       <c r="G2130" t="n">
-        <v>101.340560913086</v>
+        <v>101.34056854248</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>106</v>
       </c>
       <c r="G2131" t="n">
-        <v>102.305717468262</v>
+        <v>102.305709838867</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>109</v>
       </c>
       <c r="G2136" t="n">
-        <v>105.201156616211</v>
+        <v>105.201164245605</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>109.5</v>
       </c>
       <c r="G2138" t="n">
-        <v>105.683731079102</v>
+        <v>105.683738708496</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>108.699996948242</v>
       </c>
       <c r="G2147" t="n">
-        <v>104.911613464355</v>
+        <v>104.911605834961</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>106</v>
       </c>
       <c r="G2149" t="n">
-        <v>102.305717468262</v>
+        <v>102.305709838867</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>105</v>
       </c>
       <c r="G2151" t="n">
-        <v>101.340560913086</v>
+        <v>101.34056854248</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56347,7 +56347,7 @@
         <v>106.099998474121</v>
       </c>
       <c r="G2153" t="n">
-        <v>102.402229309082</v>
+        <v>102.402221679688</v>
       </c>
       <c r="H2153" t="s">
         <v>8</v>
@@ -56529,7 +56529,7 @@
         <v>115.199996948242</v>
       </c>
       <c r="G2160" t="n">
-        <v>111.185073852539</v>
+        <v>111.185081481934</v>
       </c>
       <c r="H2160" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G2162" t="n">
-        <v>111.281593322754</v>
+        <v>111.281600952148</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>119.699996948242</v>
       </c>
       <c r="G2165" t="n">
-        <v>115.52823638916</v>
+        <v>115.528244018555</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G2171" t="n">
-        <v>115.62476348877</v>
+        <v>115.624755859375</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>120</v>
       </c>
       <c r="G2174" t="n">
-        <v>115.817794799805</v>
+        <v>115.81778717041</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G2176" t="n">
-        <v>100.568450927734</v>
+        <v>100.56844329834</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -56997,7 +56997,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G2178" t="n">
-        <v>99.7963333129883</v>
+        <v>99.7963256835938</v>
       </c>
       <c r="H2178" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G2180" t="n">
-        <v>97.5764923095703</v>
+        <v>97.5764846801758</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>98.4499969482422</v>
       </c>
       <c r="G2181" t="n">
-        <v>95.0188369750977</v>
+        <v>95.0188446044922</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>99.8499984741211</v>
       </c>
       <c r="G2183" t="n">
-        <v>96.3700561523438</v>
+        <v>96.3700485229492</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>101.5</v>
       </c>
       <c r="G2185" t="n">
-        <v>97.9625549316406</v>
+        <v>97.9625473022461</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57231,7 +57231,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2187" t="n">
-        <v>95.260124206543</v>
+        <v>95.2601318359375</v>
       </c>
       <c r="H2187" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>94.6500015258789</v>
       </c>
       <c r="G2190" t="n">
-        <v>91.3512878417969</v>
+        <v>91.3512802124023</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57491,7 +57491,7 @@
         <v>97.9499969482422</v>
       </c>
       <c r="G2197" t="n">
-        <v>94.5362777709961</v>
+        <v>94.5362701416016</v>
       </c>
       <c r="H2197" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>97.9499969482422</v>
       </c>
       <c r="G2201" t="n">
-        <v>94.5362777709961</v>
+        <v>94.5362701416016</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57829,7 +57829,7 @@
         <v>91.1999969482422</v>
       </c>
       <c r="G2210" t="n">
-        <v>88.0215148925781</v>
+        <v>88.0215225219727</v>
       </c>
       <c r="H2210" t="s">
         <v>8</v>
@@ -57855,7 +57855,7 @@
         <v>89.6500015258789</v>
       </c>
       <c r="G2211" t="n">
-        <v>86.5255432128906</v>
+        <v>86.5255508422852</v>
       </c>
       <c r="H2211" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>86.4000015258789</v>
       </c>
       <c r="G2213" t="n">
-        <v>83.3888168334961</v>
+        <v>83.3888092041016</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57959,7 +57959,7 @@
         <v>88.1999969482422</v>
       </c>
       <c r="G2215" t="n">
-        <v>85.1260757446289</v>
+        <v>85.1260681152344</v>
       </c>
       <c r="H2215" t="s">
         <v>8</v>
@@ -57985,7 +57985,7 @@
         <v>92.25</v>
       </c>
       <c r="G2216" t="n">
-        <v>89.0349273681641</v>
+        <v>89.0349349975586</v>
       </c>
       <c r="H2216" t="s">
         <v>8</v>
@@ -58115,7 +58115,7 @@
         <v>89.3000030517578</v>
       </c>
       <c r="G2221" t="n">
-        <v>86.1877365112305</v>
+        <v>86.187744140625</v>
       </c>
       <c r="H2221" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>94</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>24407</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>92.5999984741211</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>94.0999984741211</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>93.0500030517578</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>93.0500030517578</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>93.8000030517578</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>93.4499969482422</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>23614</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>96.8000030517578</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>92.9000015258789</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>94</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>96.0500030517578</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>10228</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>93.3499984741211</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>95.75</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>94.5</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>18687</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>93.9499969482422</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>92.6999969482422</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>93.6500015258789</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>93.6500015258789</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>93.5</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>17360</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>93.0999984741211</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SES.MI.xlsx
+++ b/data/SES.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>20198</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>96.4499969482422</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>93</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>94.4499969482422</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>95.3499984741211</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
